--- a/data/base_dashboard_actividad_economica_ecuador.xlsx
+++ b/data/base_dashboard_actividad_economica_ecuador.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ARIANA_CIP_respaldo_2025\Ariana\DT\2026\Dashboards AB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8930B1F9-0955-4A60-A3F7-B630959F91F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60F0F097-25EA-48DC-A14F-203465AB36AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_LEEME" sheetId="1" r:id="rId1"/>
@@ -18,26 +18,15 @@
     <sheet name="02_Contribucion_PIB" sheetId="3" r:id="rId3"/>
     <sheet name="03_Componentes_PIB" sheetId="4" r:id="rId4"/>
     <sheet name="04_Industrias" sheetId="5" r:id="rId5"/>
+    <sheet name="05_Proyecciones" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4219" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4496" uniqueCount="204">
   <si>
     <t>Base para dashboard de actividad económica del Ecuador</t>
   </si>
@@ -60,12 +49,6 @@
     <t>Datos trimestrales ajustados de estacionalidad para PIB y componentes.</t>
   </si>
   <si>
-    <t>Fuente principal</t>
-  </si>
-  <si>
-    <t>Banco Central del Ecuador (archivo tou_135_202601).</t>
-  </si>
-  <si>
     <t>Cobertura PIB y demanda</t>
   </si>
   <si>
@@ -75,7 +58,7 @@
     <t>Cobertura industrias</t>
   </si>
   <si>
-    <t>2024.I–2025.IV, tomada de la presentación adjunta (págs. 19–20).</t>
+    <t>2024.I–2026.I, según VAB.xlsx adjunto.</t>
   </si>
   <si>
     <t>Unidades</t>
@@ -87,10 +70,16 @@
     <t>Estructura</t>
   </si>
   <si>
-    <t>03_Componentes_PIB y 04_Industrias están en formato largo (tidy) para Streamlit/Plotly.</t>
+    <t>03_Componentes_PIB, 04_Industrias y 05_Proyecciones están en formato tidy para Streamlit/Plotly.</t>
   </si>
   <si>
-    <t>Nota: el Excel fuente adjunto no contiene la serie histórica sectorial por industria. Por eso la hoja 04 reproduce el histórico disponible en la presentación (2024.I–2025.IV). Para ampliar hacia atrás o incorporar 2026.I se requiere la base sectorial trimestral del BCE.</t>
+    <t>Proyecciones</t>
+  </si>
+  <si>
+    <t>Incluye histórico BCE, proyecciones de Ecuador y comparativo regional 2026 (BCE, FMI, Banco Mundial y CEPAL según disponibilidad del archivo adjunto).</t>
+  </si>
+  <si>
+    <t>La pestaña 04_Industrias fue actualizada con la base VAB.xlsx e incorpora 2026.I. Las tasas del archivo VAB fueron convertidas de formato decimal a porcentaje (ej.: 0.045 = 4.5%).</t>
   </si>
   <si>
     <t>trimestre</t>
@@ -498,28 +487,25 @@
     <t>Resto de industrias</t>
   </si>
   <si>
-    <t>Actividades financieras y de seguros</t>
+    <t>Actividades profesionales técnicas</t>
   </si>
   <si>
-    <t>Serie trimestral de la presentación</t>
+    <t>Archivo VAB.xlsx proporcionado por la usuaria</t>
   </si>
   <si>
-    <t>BCE / CIP-DT</t>
+    <t>Agricultura ganadería y silvicultura</t>
   </si>
   <si>
-    <t>Presentación adjunta, págs. 19–20</t>
+    <t>Actividades financieras y de seguros</t>
   </si>
   <si>
     <t>Manufactura de productos alimenticios</t>
   </si>
   <si>
-    <t>Manufactura de productos no alimenticios</t>
+    <t>Información y comunicación</t>
   </si>
   <si>
-    <t>Actividades profesionales técnicas</t>
-  </si>
-  <si>
-    <t>Agricultura, ganadería y silvicultura</t>
+    <t>Manufactura de productos no alimenticios</t>
   </si>
   <si>
     <t>Comercio</t>
@@ -528,16 +514,10 @@
     <t>Alojamiento y comidas</t>
   </si>
   <si>
-    <t>Transporte y almacenamiento</t>
+    <t>Actividades inmobiliarias</t>
   </si>
   <si>
-    <t>Información y comunicación</t>
-  </si>
-  <si>
-    <t>Construcción</t>
-  </si>
-  <si>
-    <t>Actividades inmobiliarias</t>
+    <t>Transporte y almacenamiento</t>
   </si>
   <si>
     <t>Pesca y acuicultura</t>
@@ -546,7 +526,10 @@
     <t>Actividades de los hogares como empleadores</t>
   </si>
   <si>
-    <t>Arte, entretenimiento y otras actividades de servicios</t>
+    <t>Construcción</t>
+  </si>
+  <si>
+    <t>Arte entretenimiento y otras actividades de servicios</t>
   </si>
   <si>
     <t>Público</t>
@@ -576,7 +559,85 @@
     <t>Total</t>
   </si>
   <si>
-    <t>TOTAL</t>
+    <t>VAB TOTAL</t>
+  </si>
+  <si>
+    <t>tipo</t>
+  </si>
+  <si>
+    <t>pais</t>
+  </si>
+  <si>
+    <t>organismo</t>
+  </si>
+  <si>
+    <t>crecimiento_pib_pct</t>
+  </si>
+  <si>
+    <t>fecha_proyeccion</t>
+  </si>
+  <si>
+    <t>nota</t>
+  </si>
+  <si>
+    <t>fuente_detalle</t>
+  </si>
+  <si>
+    <t>Histórico</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Serie histórica</t>
+  </si>
+  <si>
+    <t>Proyección Ecuador</t>
+  </si>
+  <si>
+    <t>Según archivo de proyecciones adjunto</t>
+  </si>
+  <si>
+    <t>FMI</t>
+  </si>
+  <si>
+    <t>Banco Mundial</t>
+  </si>
+  <si>
+    <t>CEPAL</t>
+  </si>
+  <si>
+    <t>Comparativo regional</t>
+  </si>
+  <si>
+    <t>Perú</t>
+  </si>
+  <si>
+    <t>2026-01-01</t>
+  </si>
+  <si>
+    <t>Comparativo regional 2026 del archivo adjunto</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>Nota (1) del archivo fuente</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Nota (2) del archivo fuente</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Chile</t>
   </si>
 </sst>
 </file>
@@ -607,7 +668,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -617,6 +678,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F6F9"/>
       </patternFill>
     </fill>
     <fill>
@@ -642,14 +713,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -728,7 +805,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tbl_industrias" displayName="tbl_industrias" ref="A1:K169" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tbl_industrias" displayName="tbl_industrias" ref="A1:K190" totalsRowShown="0">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="trimestre"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="anio"/>
@@ -741,6 +818,22 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="ajuste"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="fuente"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="nota_fuente"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="tbl_proyecciones" displayName="tbl_proyecciones" ref="A1:H32" totalsRowShown="0">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="tipo"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="pais"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="anio"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="organismo"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="crecimiento_pib_pct"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="fecha_proyeccion"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="nota"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="fuente_detalle"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -949,16 +1042,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
@@ -1025,16 +1118,16 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="14.5">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -28579,7 +28672,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:K169"/>
+  <dimension ref="A1:K190"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -28590,43 +28683,43 @@
     <col min="6" max="6" width="44" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="32" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="32" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>151</v>
       </c>
     </row>
@@ -28650,19 +28743,19 @@
         <v>153</v>
       </c>
       <c r="G2" s="2">
-        <v>1.5</v>
+        <v>4.5363182991722928</v>
       </c>
       <c r="H2" s="2">
-        <v>2.4</v>
+        <v>-2.9000864858508391</v>
       </c>
       <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" t="s">
         <v>154</v>
-      </c>
-      <c r="J2" t="s">
-        <v>155</v>
-      </c>
-      <c r="K2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -28685,19 +28778,19 @@
         <v>153</v>
       </c>
       <c r="G3" s="2">
-        <v>1.5</v>
+        <v>-3.2715038001893459</v>
       </c>
       <c r="H3" s="2">
-        <v>1.2</v>
+        <v>-3.740542856650686</v>
       </c>
       <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s">
         <v>154</v>
-      </c>
-      <c r="J3" t="s">
-        <v>155</v>
-      </c>
-      <c r="K3" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -28720,19 +28813,19 @@
         <v>153</v>
       </c>
       <c r="G4" s="2">
-        <v>2.5</v>
+        <v>3.2725546571104491</v>
       </c>
       <c r="H4" s="2">
-        <v>2.2999999999999998</v>
+        <v>3.8901096781733369</v>
       </c>
       <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" t="s">
         <v>154</v>
-      </c>
-      <c r="J4" t="s">
-        <v>155</v>
-      </c>
-      <c r="K4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -28755,19 +28848,19 @@
         <v>153</v>
       </c>
       <c r="G5" s="2">
-        <v>10.5</v>
+        <v>-7.9431739190155</v>
       </c>
       <c r="H5" s="2">
-        <v>4.2</v>
+        <v>-5.1975543102347306</v>
       </c>
       <c r="I5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" t="s">
         <v>154</v>
-      </c>
-      <c r="J5" t="s">
-        <v>155</v>
-      </c>
-      <c r="K5" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -28790,19 +28883,19 @@
         <v>153</v>
       </c>
       <c r="G6" s="2">
-        <v>10.199999999999999</v>
+        <v>0.1200305391588552</v>
       </c>
       <c r="H6" s="2">
-        <v>2.1</v>
+        <v>5.604839100513237</v>
       </c>
       <c r="I6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" t="s">
         <v>154</v>
-      </c>
-      <c r="J6" t="s">
-        <v>155</v>
-      </c>
-      <c r="K6" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -28825,19 +28918,19 @@
         <v>153</v>
       </c>
       <c r="G7" s="2">
-        <v>10.6</v>
+        <v>6.441306247712264</v>
       </c>
       <c r="H7" s="2">
-        <v>1.6</v>
+        <v>2.3369879319641074</v>
       </c>
       <c r="I7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" t="s">
         <v>154</v>
-      </c>
-      <c r="J7" t="s">
-        <v>155</v>
-      </c>
-      <c r="K7" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -28860,19 +28953,19 @@
         <v>153</v>
       </c>
       <c r="G8" s="2">
-        <v>10</v>
+        <v>4.6668196152387376</v>
       </c>
       <c r="H8" s="2">
-        <v>1.7</v>
+        <v>2.1581541303796969</v>
       </c>
       <c r="I8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" t="s">
         <v>154</v>
-      </c>
-      <c r="J8" t="s">
-        <v>155</v>
-      </c>
-      <c r="K8" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -28895,2259 +28988,2259 @@
         <v>153</v>
       </c>
       <c r="G9" s="2">
-        <v>8.6999999999999993</v>
+        <v>6.71669517070832</v>
       </c>
       <c r="H9" s="2">
-        <v>3</v>
+        <v>-3.340870246148675</v>
       </c>
       <c r="I9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" t="s">
         <v>154</v>
-      </c>
-      <c r="J9" t="s">
-        <v>155</v>
-      </c>
-      <c r="K9" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B10">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>8097</v>
+        <v>8105</v>
       </c>
       <c r="E10" t="s">
         <v>152</v>
       </c>
       <c r="F10" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G10" s="2">
-        <v>-6.9</v>
+        <v>4.5007171370037069</v>
       </c>
       <c r="H10" s="2">
-        <v>-2.6</v>
+        <v>3.4119488191443725</v>
       </c>
       <c r="I10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" t="s">
         <v>154</v>
-      </c>
-      <c r="J10" t="s">
-        <v>155</v>
-      </c>
-      <c r="K10" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B11">
         <v>2024</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>8098</v>
+        <v>8097</v>
       </c>
       <c r="E11" t="s">
         <v>152</v>
       </c>
       <c r="F11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G11" s="2">
-        <v>-0.2</v>
+        <v>-0.57481928610693123</v>
       </c>
       <c r="H11" s="2">
-        <v>9</v>
+        <v>3.3835391378729929</v>
       </c>
       <c r="I11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" t="s">
         <v>154</v>
-      </c>
-      <c r="J11" t="s">
-        <v>155</v>
-      </c>
-      <c r="K11" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B12">
         <v>2024</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>8099</v>
+        <v>8098</v>
       </c>
       <c r="E12" t="s">
         <v>152</v>
       </c>
       <c r="F12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G12" s="2">
-        <v>-1.4</v>
+        <v>-6.5620197394108963</v>
       </c>
       <c r="H12" s="2">
-        <v>-5.9</v>
+        <v>-1.4039257244433556</v>
       </c>
       <c r="I12" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" t="s">
         <v>154</v>
-      </c>
-      <c r="J12" t="s">
-        <v>155</v>
-      </c>
-      <c r="K12" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B13">
         <v>2024</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13">
-        <v>8100</v>
+        <v>8099</v>
       </c>
       <c r="E13" t="s">
         <v>152</v>
       </c>
       <c r="F13" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G13" s="2">
-        <v>4.9000000000000004</v>
+        <v>-2.0711065302285614</v>
       </c>
       <c r="H13" s="2">
-        <v>5</v>
+        <v>1.7744718219988798</v>
       </c>
       <c r="I13" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" t="s">
         <v>154</v>
-      </c>
-      <c r="J13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K13" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>8101</v>
+        <v>8100</v>
       </c>
       <c r="E14" t="s">
         <v>152</v>
       </c>
       <c r="F14" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G14" s="2">
-        <v>12.6</v>
+        <v>10.762892482052489</v>
       </c>
       <c r="H14" s="2">
-        <v>4.4000000000000004</v>
+        <v>6.7688125401434984</v>
       </c>
       <c r="I14" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" t="s">
         <v>154</v>
-      </c>
-      <c r="J14" t="s">
-        <v>155</v>
-      </c>
-      <c r="K14" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B15">
         <v>2025</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>8102</v>
+        <v>8101</v>
       </c>
       <c r="E15" t="s">
         <v>152</v>
       </c>
       <c r="F15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G15" s="2">
-        <v>3.6</v>
+        <v>15.167821195535858</v>
       </c>
       <c r="H15" s="2">
-        <v>0.3</v>
+        <v>7.4949983986875912</v>
       </c>
       <c r="I15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" t="s">
         <v>154</v>
-      </c>
-      <c r="J15" t="s">
-        <v>155</v>
-      </c>
-      <c r="K15" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B16">
         <v>2025</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>8103</v>
+        <v>8102</v>
       </c>
       <c r="E16" t="s">
         <v>152</v>
       </c>
       <c r="F16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G16" s="2">
-        <v>10.5</v>
+        <v>8.8117271345844017</v>
       </c>
       <c r="H16" s="2">
-        <v>0.4</v>
+        <v>-6.8454276616206293</v>
       </c>
       <c r="I16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16" t="s">
         <v>154</v>
-      </c>
-      <c r="J16" t="s">
-        <v>155</v>
-      </c>
-      <c r="K16" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B17">
         <v>2025</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17">
-        <v>8104</v>
+        <v>8103</v>
       </c>
       <c r="E17" t="s">
         <v>152</v>
       </c>
       <c r="F17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G17" s="2">
-        <v>7.7</v>
+        <v>5.3598714469114128</v>
       </c>
       <c r="H17" s="2">
-        <v>2.2999999999999998</v>
+        <v>-1.4541396399270989</v>
       </c>
       <c r="I17" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" t="s">
+        <v>29</v>
+      </c>
+      <c r="K17" t="s">
         <v>154</v>
-      </c>
-      <c r="J17" t="s">
-        <v>155</v>
-      </c>
-      <c r="K17" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B18">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18">
-        <v>8097</v>
+        <v>8104</v>
       </c>
       <c r="E18" t="s">
         <v>152</v>
       </c>
       <c r="F18" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G18" s="2">
-        <v>-2.5</v>
+        <v>5.4225401182691035</v>
       </c>
       <c r="H18" s="2">
-        <v>0.4</v>
+        <v>6.832319257952113</v>
       </c>
       <c r="I18" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K18" t="s">
         <v>154</v>
-      </c>
-      <c r="J18" t="s">
-        <v>155</v>
-      </c>
-      <c r="K18" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B19">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>8098</v>
+        <v>8105</v>
       </c>
       <c r="E19" t="s">
         <v>152</v>
       </c>
       <c r="F19" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G19" s="2">
-        <v>-11.5</v>
+        <v>-3.8263225496385944</v>
       </c>
       <c r="H19" s="2">
-        <v>-4.7</v>
+        <v>-1.9356838497296858</v>
       </c>
       <c r="I19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19" t="s">
         <v>154</v>
-      </c>
-      <c r="J19" t="s">
-        <v>155</v>
-      </c>
-      <c r="K19" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B20">
         <v>2024</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>8099</v>
+        <v>8097</v>
       </c>
       <c r="E20" t="s">
         <v>152</v>
       </c>
       <c r="F20" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G20" s="2">
-        <v>-6.5</v>
+        <v>1.491702368350234</v>
       </c>
       <c r="H20" s="2">
-        <v>-0.3</v>
+        <v>2.3603355275160665</v>
       </c>
       <c r="I20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" t="s">
         <v>154</v>
-      </c>
-      <c r="J20" t="s">
-        <v>155</v>
-      </c>
-      <c r="K20" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B21">
         <v>2024</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>8100</v>
+        <v>8098</v>
       </c>
       <c r="E21" t="s">
         <v>152</v>
       </c>
       <c r="F21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G21" s="2">
-        <v>-4.9000000000000004</v>
+        <v>1.5017076736108637</v>
       </c>
       <c r="H21" s="2">
-        <v>-0.3</v>
+        <v>1.2367861327921448</v>
       </c>
       <c r="I21" t="s">
+        <v>28</v>
+      </c>
+      <c r="J21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" t="s">
         <v>154</v>
-      </c>
-      <c r="J21" t="s">
-        <v>155</v>
-      </c>
-      <c r="K21" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B22">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22">
-        <v>8101</v>
+        <v>8099</v>
       </c>
       <c r="E22" t="s">
         <v>152</v>
       </c>
       <c r="F22" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G22" s="2">
-        <v>0.9</v>
+        <v>2.5340286361074327</v>
       </c>
       <c r="H22" s="2">
-        <v>6.5</v>
+        <v>2.2977534156689572</v>
       </c>
       <c r="I22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" t="s">
         <v>154</v>
-      </c>
-      <c r="J22" t="s">
-        <v>155</v>
-      </c>
-      <c r="K22" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B23">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>8102</v>
+        <v>8100</v>
       </c>
       <c r="E23" t="s">
         <v>152</v>
       </c>
       <c r="F23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G23" s="2">
-        <v>2.2999999999999998</v>
+        <v>10.49963297453913</v>
       </c>
       <c r="H23" s="2">
-        <v>-3.4</v>
+        <v>4.2376685202622832</v>
       </c>
       <c r="I23" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" t="s">
         <v>154</v>
-      </c>
-      <c r="J23" t="s">
-        <v>155</v>
-      </c>
-      <c r="K23" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B24">
         <v>2025</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>8103</v>
+        <v>8101</v>
       </c>
       <c r="E24" t="s">
         <v>152</v>
       </c>
       <c r="F24" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G24" s="2">
-        <v>6.9</v>
+        <v>10.170479944089328</v>
       </c>
       <c r="H24" s="2">
-        <v>4.2</v>
+        <v>2.0554275949756562</v>
       </c>
       <c r="I24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J24" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24" t="s">
         <v>154</v>
-      </c>
-      <c r="J24" t="s">
-        <v>155</v>
-      </c>
-      <c r="K24" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B25">
         <v>2025</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>8104</v>
+        <v>8102</v>
       </c>
       <c r="E25" t="s">
         <v>152</v>
       </c>
       <c r="F25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G25" s="2">
-        <v>7.1</v>
+        <v>10.588303790144371</v>
       </c>
       <c r="H25" s="2">
-        <v>-0.1</v>
+        <v>1.6207287584911523</v>
       </c>
       <c r="I25" t="s">
+        <v>28</v>
+      </c>
+      <c r="J25" t="s">
+        <v>29</v>
+      </c>
+      <c r="K25" t="s">
         <v>154</v>
-      </c>
-      <c r="J25" t="s">
-        <v>155</v>
-      </c>
-      <c r="K25" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B26">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26">
-        <v>8097</v>
+        <v>8103</v>
       </c>
       <c r="E26" t="s">
         <v>152</v>
       </c>
       <c r="F26" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G26" s="2">
-        <v>4.5</v>
+        <v>9.9536913537601848</v>
       </c>
       <c r="H26" s="2">
-        <v>-2.9</v>
+        <v>1.7107164116930251</v>
       </c>
       <c r="I26" t="s">
+        <v>28</v>
+      </c>
+      <c r="J26" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" t="s">
         <v>154</v>
-      </c>
-      <c r="J26" t="s">
-        <v>155</v>
-      </c>
-      <c r="K26" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B27">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27">
-        <v>8098</v>
+        <v>8104</v>
       </c>
       <c r="E27" t="s">
         <v>152</v>
       </c>
       <c r="F27" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G27" s="2">
-        <v>-3.3</v>
+        <v>8.6748813139916336</v>
       </c>
       <c r="H27" s="2">
-        <v>-3.7</v>
+        <v>3.0253383530385092</v>
       </c>
       <c r="I27" t="s">
+        <v>28</v>
+      </c>
+      <c r="J27" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" t="s">
         <v>154</v>
-      </c>
-      <c r="J27" t="s">
-        <v>155</v>
-      </c>
-      <c r="K27" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B28">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>8099</v>
+        <v>8105</v>
       </c>
       <c r="E28" t="s">
         <v>152</v>
       </c>
       <c r="F28" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G28" s="2">
-        <v>3.3</v>
+        <v>12.014702106993314</v>
       </c>
       <c r="H28" s="2">
-        <v>3.9</v>
+        <v>5.1918178536921822</v>
       </c>
       <c r="I28" t="s">
+        <v>28</v>
+      </c>
+      <c r="J28" t="s">
+        <v>29</v>
+      </c>
+      <c r="K28" t="s">
         <v>154</v>
-      </c>
-      <c r="J28" t="s">
-        <v>155</v>
-      </c>
-      <c r="K28" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B29">
         <v>2024</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>8100</v>
+        <v>8097</v>
       </c>
       <c r="E29" t="s">
         <v>152</v>
       </c>
       <c r="F29" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G29" s="2">
-        <v>-7.9</v>
+        <v>-6.9476240426026292</v>
       </c>
       <c r="H29" s="2">
-        <v>-5.2</v>
+        <v>-2.6294781816594393</v>
       </c>
       <c r="I29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J29" t="s">
+        <v>29</v>
+      </c>
+      <c r="K29" t="s">
         <v>154</v>
-      </c>
-      <c r="J29" t="s">
-        <v>155</v>
-      </c>
-      <c r="K29" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B30">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30">
-        <v>8101</v>
+        <v>8098</v>
       </c>
       <c r="E30" t="s">
         <v>152</v>
       </c>
       <c r="F30" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G30" s="2">
-        <v>0.1</v>
+        <v>-0.20924791689497235</v>
       </c>
       <c r="H30" s="2">
-        <v>5.6</v>
+        <v>9.0191986417856853</v>
       </c>
       <c r="I30" t="s">
+        <v>28</v>
+      </c>
+      <c r="J30" t="s">
+        <v>29</v>
+      </c>
+      <c r="K30" t="s">
         <v>154</v>
-      </c>
-      <c r="J30" t="s">
-        <v>155</v>
-      </c>
-      <c r="K30" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B31">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31">
-        <v>8102</v>
+        <v>8099</v>
       </c>
       <c r="E31" t="s">
         <v>152</v>
       </c>
       <c r="F31" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G31" s="2">
-        <v>6.4</v>
+        <v>-1.3659618058765144</v>
       </c>
       <c r="H31" s="2">
-        <v>2.2999999999999998</v>
+        <v>-5.8665538165694535</v>
       </c>
       <c r="I31" t="s">
+        <v>28</v>
+      </c>
+      <c r="J31" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" t="s">
         <v>154</v>
-      </c>
-      <c r="J31" t="s">
-        <v>155</v>
-      </c>
-      <c r="K31" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B32">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32">
-        <v>8103</v>
+        <v>8100</v>
       </c>
       <c r="E32" t="s">
         <v>152</v>
       </c>
       <c r="F32" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G32" s="2">
-        <v>4.7</v>
+        <v>4.9405568565057401</v>
       </c>
       <c r="H32" s="2">
-        <v>2.2000000000000002</v>
+        <v>5.0192526269299487</v>
       </c>
       <c r="I32" t="s">
+        <v>28</v>
+      </c>
+      <c r="J32" t="s">
+        <v>29</v>
+      </c>
+      <c r="K32" t="s">
         <v>154</v>
-      </c>
-      <c r="J32" t="s">
-        <v>155</v>
-      </c>
-      <c r="K32" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B33">
         <v>2025</v>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>8104</v>
+        <v>8101</v>
       </c>
       <c r="E33" t="s">
         <v>152</v>
       </c>
       <c r="F33" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G33" s="2">
-        <v>6.7</v>
+        <v>12.568958118053342</v>
       </c>
       <c r="H33" s="2">
-        <v>-3.3</v>
+        <v>4.4486375986126703</v>
       </c>
       <c r="I33" t="s">
+        <v>28</v>
+      </c>
+      <c r="J33" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33" t="s">
         <v>154</v>
-      </c>
-      <c r="J33" t="s">
-        <v>155</v>
-      </c>
-      <c r="K33" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B34">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>8097</v>
+        <v>8102</v>
       </c>
       <c r="E34" t="s">
         <v>152</v>
       </c>
       <c r="F34" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G34" s="2">
-        <v>-0.6</v>
+        <v>3.5571031614691773</v>
       </c>
       <c r="H34" s="2">
-        <v>3.4</v>
+        <v>0.29152431604058116</v>
       </c>
       <c r="I34" t="s">
+        <v>28</v>
+      </c>
+      <c r="J34" t="s">
+        <v>29</v>
+      </c>
+      <c r="K34" t="s">
         <v>154</v>
-      </c>
-      <c r="J34" t="s">
-        <v>155</v>
-      </c>
-      <c r="K34" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B35">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35">
-        <v>8098</v>
+        <v>8103</v>
       </c>
       <c r="E35" t="s">
         <v>152</v>
       </c>
       <c r="F35" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G35" s="2">
-        <v>-6.6</v>
+        <v>10.498081551035021</v>
       </c>
       <c r="H35" s="2">
-        <v>-1.4</v>
+        <v>0.44279818100221302</v>
       </c>
       <c r="I35" t="s">
+        <v>28</v>
+      </c>
+      <c r="J35" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35" t="s">
         <v>154</v>
-      </c>
-      <c r="J35" t="s">
-        <v>155</v>
-      </c>
-      <c r="K35" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B36">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36">
-        <v>8099</v>
+        <v>8104</v>
       </c>
       <c r="E36" t="s">
         <v>152</v>
       </c>
       <c r="F36" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G36" s="2">
-        <v>-2.1</v>
+        <v>7.6681164077042618</v>
       </c>
       <c r="H36" s="2">
-        <v>1.8</v>
+        <v>2.3296057105208767</v>
       </c>
       <c r="I36" t="s">
+        <v>28</v>
+      </c>
+      <c r="J36" t="s">
+        <v>29</v>
+      </c>
+      <c r="K36" t="s">
         <v>154</v>
-      </c>
-      <c r="J36" t="s">
-        <v>155</v>
-      </c>
-      <c r="K36" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B37">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>8100</v>
+        <v>8105</v>
       </c>
       <c r="E37" t="s">
         <v>152</v>
       </c>
       <c r="F37" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G37" s="2">
-        <v>10.8</v>
+        <v>3.1595340632313285</v>
       </c>
       <c r="H37" s="2">
-        <v>6.8</v>
+        <v>7.487033033286572E-2</v>
       </c>
       <c r="I37" t="s">
+        <v>28</v>
+      </c>
+      <c r="J37" t="s">
+        <v>29</v>
+      </c>
+      <c r="K37" t="s">
         <v>154</v>
-      </c>
-      <c r="J37" t="s">
-        <v>155</v>
-      </c>
-      <c r="K37" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B38">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
       <c r="D38">
-        <v>8101</v>
+        <v>8097</v>
       </c>
       <c r="E38" t="s">
         <v>152</v>
       </c>
       <c r="F38" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G38" s="2">
-        <v>15.2</v>
+        <v>-2.1612135009641209</v>
       </c>
       <c r="H38" s="2">
-        <v>7.5</v>
+        <v>-5.1466693848519096</v>
       </c>
       <c r="I38" t="s">
+        <v>28</v>
+      </c>
+      <c r="J38" t="s">
+        <v>29</v>
+      </c>
+      <c r="K38" t="s">
         <v>154</v>
-      </c>
-      <c r="J38" t="s">
-        <v>155</v>
-      </c>
-      <c r="K38" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B39">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C39">
         <v>2</v>
       </c>
       <c r="D39">
-        <v>8102</v>
+        <v>8098</v>
       </c>
       <c r="E39" t="s">
         <v>152</v>
       </c>
       <c r="F39" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G39" s="2">
-        <v>8.8000000000000007</v>
+        <v>-3.7150763202043247</v>
       </c>
       <c r="H39" s="2">
-        <v>-6.8</v>
+        <v>-0.59904884398006564</v>
       </c>
       <c r="I39" t="s">
+        <v>28</v>
+      </c>
+      <c r="J39" t="s">
+        <v>29</v>
+      </c>
+      <c r="K39" t="s">
         <v>154</v>
-      </c>
-      <c r="J39" t="s">
-        <v>155</v>
-      </c>
-      <c r="K39" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B40">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40">
-        <v>8103</v>
+        <v>8099</v>
       </c>
       <c r="E40" t="s">
         <v>152</v>
       </c>
       <c r="F40" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G40" s="2">
-        <v>5.4</v>
+        <v>0.28346704561117431</v>
       </c>
       <c r="H40" s="2">
-        <v>-1.5</v>
+        <v>3.139848065852946</v>
       </c>
       <c r="I40" t="s">
+        <v>28</v>
+      </c>
+      <c r="J40" t="s">
+        <v>29</v>
+      </c>
+      <c r="K40" t="s">
         <v>154</v>
-      </c>
-      <c r="J40" t="s">
-        <v>155</v>
-      </c>
-      <c r="K40" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B41">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C41">
         <v>4</v>
       </c>
       <c r="D41">
-        <v>8104</v>
+        <v>8100</v>
       </c>
       <c r="E41" t="s">
         <v>152</v>
       </c>
       <c r="F41" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G41" s="2">
-        <v>5.4</v>
+        <v>-1.5280012758321138</v>
       </c>
       <c r="H41" s="2">
-        <v>6.8</v>
+        <v>1.261216528024578</v>
       </c>
       <c r="I41" t="s">
+        <v>28</v>
+      </c>
+      <c r="J41" t="s">
+        <v>29</v>
+      </c>
+      <c r="K41" t="s">
         <v>154</v>
-      </c>
-      <c r="J41" t="s">
-        <v>155</v>
-      </c>
-      <c r="K41" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B42">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C42">
         <v>1</v>
       </c>
       <c r="D42">
-        <v>8097</v>
+        <v>8101</v>
       </c>
       <c r="E42" t="s">
         <v>152</v>
       </c>
       <c r="F42" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G42" s="2">
-        <v>-2.1</v>
+        <v>2.3159785917947318</v>
       </c>
       <c r="H42" s="2">
-        <v>-1.1000000000000001</v>
+        <v>-1.4439488349896945</v>
       </c>
       <c r="I42" t="s">
+        <v>28</v>
+      </c>
+      <c r="J42" t="s">
+        <v>29</v>
+      </c>
+      <c r="K42" t="s">
         <v>154</v>
-      </c>
-      <c r="J42" t="s">
-        <v>155</v>
-      </c>
-      <c r="K42" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B43">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C43">
         <v>2</v>
       </c>
       <c r="D43">
-        <v>8098</v>
+        <v>8102</v>
       </c>
       <c r="E43" t="s">
         <v>152</v>
       </c>
       <c r="F43" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G43" s="2">
-        <v>-6.8</v>
+        <v>5.5509491170966818</v>
       </c>
       <c r="H43" s="2">
-        <v>-1.6</v>
+        <v>2.5437559417671674</v>
       </c>
       <c r="I43" t="s">
+        <v>28</v>
+      </c>
+      <c r="J43" t="s">
+        <v>29</v>
+      </c>
+      <c r="K43" t="s">
         <v>154</v>
-      </c>
-      <c r="J43" t="s">
-        <v>155</v>
-      </c>
-      <c r="K43" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B44">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C44">
         <v>3</v>
       </c>
       <c r="D44">
-        <v>8099</v>
+        <v>8103</v>
       </c>
       <c r="E44" t="s">
         <v>152</v>
       </c>
       <c r="F44" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G44" s="2">
-        <v>-4.0999999999999996</v>
+        <v>2.4419112226984341</v>
       </c>
       <c r="H44" s="2">
-        <v>-1.7</v>
+        <v>0.10182994530083533</v>
       </c>
       <c r="I44" t="s">
+        <v>28</v>
+      </c>
+      <c r="J44" t="s">
+        <v>29</v>
+      </c>
+      <c r="K44" t="s">
         <v>154</v>
-      </c>
-      <c r="J44" t="s">
-        <v>155</v>
-      </c>
-      <c r="K44" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B45">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C45">
         <v>4</v>
       </c>
       <c r="D45">
-        <v>8100</v>
+        <v>8104</v>
       </c>
       <c r="E45" t="s">
         <v>152</v>
       </c>
       <c r="F45" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G45" s="2">
-        <v>0.8</v>
+        <v>3.0085161928356197</v>
       </c>
       <c r="H45" s="2">
-        <v>5.5</v>
+        <v>1.8212910901067803</v>
       </c>
       <c r="I45" t="s">
+        <v>28</v>
+      </c>
+      <c r="J45" t="s">
+        <v>29</v>
+      </c>
+      <c r="K45" t="s">
         <v>154</v>
-      </c>
-      <c r="J45" t="s">
-        <v>155</v>
-      </c>
-      <c r="K45" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B46">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46">
-        <v>8101</v>
+        <v>8105</v>
       </c>
       <c r="E46" t="s">
         <v>152</v>
       </c>
       <c r="F46" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G46" s="2">
-        <v>4.8</v>
+        <v>4.9148627008156698</v>
       </c>
       <c r="H46" s="2">
-        <v>2.8</v>
+        <v>0.37999729027047291</v>
       </c>
       <c r="I46" t="s">
+        <v>28</v>
+      </c>
+      <c r="J46" t="s">
+        <v>29</v>
+      </c>
+      <c r="K46" t="s">
         <v>154</v>
-      </c>
-      <c r="J46" t="s">
-        <v>155</v>
-      </c>
-      <c r="K46" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B47">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47">
-        <v>8102</v>
+        <v>8097</v>
       </c>
       <c r="E47" t="s">
         <v>152</v>
       </c>
       <c r="F47" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G47" s="2">
-        <v>3.7</v>
+        <v>-2.495834709759126</v>
       </c>
       <c r="H47" s="2">
-        <v>-2.6</v>
+        <v>0.41865427115572729</v>
       </c>
       <c r="I47" t="s">
+        <v>28</v>
+      </c>
+      <c r="J47" t="s">
+        <v>29</v>
+      </c>
+      <c r="K47" t="s">
         <v>154</v>
-      </c>
-      <c r="J47" t="s">
-        <v>155</v>
-      </c>
-      <c r="K47" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B48">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48">
-        <v>8103</v>
+        <v>8098</v>
       </c>
       <c r="E48" t="s">
         <v>152</v>
       </c>
       <c r="F48" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G48" s="2">
-        <v>7.1</v>
+        <v>-11.463179516686516</v>
       </c>
       <c r="H48" s="2">
-        <v>1.4</v>
+        <v>-4.6826034626550879</v>
       </c>
       <c r="I48" t="s">
+        <v>28</v>
+      </c>
+      <c r="J48" t="s">
+        <v>29</v>
+      </c>
+      <c r="K48" t="s">
         <v>154</v>
-      </c>
-      <c r="J48" t="s">
-        <v>155</v>
-      </c>
-      <c r="K48" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B49">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D49">
-        <v>8104</v>
+        <v>8099</v>
       </c>
       <c r="E49" t="s">
         <v>152</v>
       </c>
       <c r="F49" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G49" s="2">
-        <v>5.0999999999999996</v>
+        <v>-6.4739152726476235</v>
       </c>
       <c r="H49" s="2">
-        <v>3.6</v>
+        <v>-0.33117311325246979</v>
       </c>
       <c r="I49" t="s">
+        <v>28</v>
+      </c>
+      <c r="J49" t="s">
+        <v>29</v>
+      </c>
+      <c r="K49" t="s">
         <v>154</v>
-      </c>
-      <c r="J49" t="s">
-        <v>155</v>
-      </c>
-      <c r="K49" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B50">
         <v>2024</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D50">
-        <v>8097</v>
+        <v>8100</v>
       </c>
       <c r="E50" t="s">
         <v>152</v>
       </c>
       <c r="F50" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G50" s="2">
-        <v>-1.5</v>
+        <v>-4.8566475098033361</v>
       </c>
       <c r="H50" s="2">
-        <v>-10.1</v>
+        <v>-0.26845776958763778</v>
       </c>
       <c r="I50" t="s">
+        <v>28</v>
+      </c>
+      <c r="J50" t="s">
+        <v>29</v>
+      </c>
+      <c r="K50" t="s">
         <v>154</v>
-      </c>
-      <c r="J50" t="s">
-        <v>155</v>
-      </c>
-      <c r="K50" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B51">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>8098</v>
+        <v>8101</v>
       </c>
       <c r="E51" t="s">
         <v>152</v>
       </c>
       <c r="F51" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G51" s="2">
-        <v>-3.3</v>
+        <v>0.89357798247020614</v>
       </c>
       <c r="H51" s="2">
-        <v>7.3</v>
+        <v>6.4877057663644822</v>
       </c>
       <c r="I51" t="s">
+        <v>28</v>
+      </c>
+      <c r="J51" t="s">
+        <v>29</v>
+      </c>
+      <c r="K51" t="s">
         <v>154</v>
-      </c>
-      <c r="J51" t="s">
-        <v>155</v>
-      </c>
-      <c r="K51" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B52">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52">
-        <v>8099</v>
+        <v>8102</v>
       </c>
       <c r="E52" t="s">
         <v>152</v>
       </c>
       <c r="F52" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G52" s="2">
-        <v>8.5</v>
+        <v>2.2674140072709292</v>
       </c>
       <c r="H52" s="2">
-        <v>1.5</v>
+        <v>-3.38469654160235</v>
       </c>
       <c r="I52" t="s">
+        <v>28</v>
+      </c>
+      <c r="J52" t="s">
+        <v>29</v>
+      </c>
+      <c r="K52" t="s">
         <v>154</v>
-      </c>
-      <c r="J52" t="s">
-        <v>155</v>
-      </c>
-      <c r="K52" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B53">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D53">
-        <v>8100</v>
+        <v>8103</v>
       </c>
       <c r="E53" t="s">
         <v>152</v>
       </c>
       <c r="F53" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G53" s="2">
-        <v>-2</v>
+        <v>6.8760890804705488</v>
       </c>
       <c r="H53" s="2">
-        <v>0.1</v>
+        <v>4.1603967822700927</v>
       </c>
       <c r="I53" t="s">
+        <v>28</v>
+      </c>
+      <c r="J53" t="s">
+        <v>29</v>
+      </c>
+      <c r="K53" t="s">
         <v>154</v>
-      </c>
-      <c r="J53" t="s">
-        <v>155</v>
-      </c>
-      <c r="K53" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B54">
         <v>2025</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D54">
-        <v>8101</v>
+        <v>8104</v>
       </c>
       <c r="E54" t="s">
         <v>152</v>
       </c>
       <c r="F54" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G54" s="2">
-        <v>4.7</v>
+        <v>7.0893386947105119</v>
       </c>
       <c r="H54" s="2">
-        <v>-4</v>
+        <v>-6.946365321257586E-2</v>
       </c>
       <c r="I54" t="s">
+        <v>28</v>
+      </c>
+      <c r="J54" t="s">
+        <v>29</v>
+      </c>
+      <c r="K54" t="s">
         <v>154</v>
-      </c>
-      <c r="J54" t="s">
-        <v>155</v>
-      </c>
-      <c r="K54" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B55">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>8102</v>
+        <v>8105</v>
       </c>
       <c r="E55" t="s">
         <v>152</v>
       </c>
       <c r="F55" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G55" s="2">
-        <v>3</v>
+        <v>2.747546546466384</v>
       </c>
       <c r="H55" s="2">
-        <v>5.6</v>
+        <v>2.1703060100826121</v>
       </c>
       <c r="I55" t="s">
+        <v>28</v>
+      </c>
+      <c r="J55" t="s">
+        <v>29</v>
+      </c>
+      <c r="K55" t="s">
         <v>154</v>
-      </c>
-      <c r="J55" t="s">
-        <v>155</v>
-      </c>
-      <c r="K55" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B56">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>8103</v>
+        <v>8097</v>
       </c>
       <c r="E56" t="s">
         <v>152</v>
       </c>
       <c r="F56" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G56" s="2">
-        <v>2.9</v>
+        <v>-2.1383771035045185</v>
       </c>
       <c r="H56" s="2">
-        <v>1.4</v>
+        <v>-1.1168066065789684</v>
       </c>
       <c r="I56" t="s">
+        <v>28</v>
+      </c>
+      <c r="J56" t="s">
+        <v>29</v>
+      </c>
+      <c r="K56" t="s">
         <v>154</v>
-      </c>
-      <c r="J56" t="s">
-        <v>155</v>
-      </c>
-      <c r="K56" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B57">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D57">
-        <v>8104</v>
+        <v>8098</v>
       </c>
       <c r="E57" t="s">
         <v>152</v>
       </c>
       <c r="F57" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G57" s="2">
-        <v>5.0999999999999996</v>
+        <v>-6.7905504240003296</v>
       </c>
       <c r="H57" s="2">
-        <v>2.2000000000000002</v>
+        <v>-1.6401262939892303</v>
       </c>
       <c r="I57" t="s">
+        <v>28</v>
+      </c>
+      <c r="J57" t="s">
+        <v>29</v>
+      </c>
+      <c r="K57" t="s">
         <v>154</v>
-      </c>
-      <c r="J57" t="s">
-        <v>155</v>
-      </c>
-      <c r="K57" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B58">
         <v>2024</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D58">
-        <v>8097</v>
+        <v>8099</v>
       </c>
       <c r="E58" t="s">
         <v>152</v>
       </c>
       <c r="F58" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G58" s="2">
-        <v>-2.5</v>
+        <v>-4.0884870669684714</v>
       </c>
       <c r="H58" s="2">
-        <v>-4.4000000000000004</v>
+        <v>-1.7467210059600724</v>
       </c>
       <c r="I58" t="s">
+        <v>28</v>
+      </c>
+      <c r="J58" t="s">
+        <v>29</v>
+      </c>
+      <c r="K58" t="s">
         <v>154</v>
-      </c>
-      <c r="J58" t="s">
-        <v>155</v>
-      </c>
-      <c r="K58" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B59">
         <v>2024</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D59">
-        <v>8098</v>
+        <v>8100</v>
       </c>
       <c r="E59" t="s">
         <v>152</v>
       </c>
       <c r="F59" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G59" s="2">
-        <v>-6.6</v>
+        <v>0.7917814908564802</v>
       </c>
       <c r="H59" s="2">
-        <v>-0.4</v>
+        <v>5.4721071850409864</v>
       </c>
       <c r="I59" t="s">
+        <v>28</v>
+      </c>
+      <c r="J59" t="s">
+        <v>29</v>
+      </c>
+      <c r="K59" t="s">
         <v>154</v>
-      </c>
-      <c r="J59" t="s">
-        <v>155</v>
-      </c>
-      <c r="K59" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B60">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D60">
-        <v>8099</v>
+        <v>8101</v>
       </c>
       <c r="E60" t="s">
         <v>152</v>
       </c>
       <c r="F60" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G60" s="2">
-        <v>-2.7</v>
+        <v>4.7845250792014182</v>
       </c>
       <c r="H60" s="2">
-        <v>0.6</v>
+        <v>2.8003305902913</v>
       </c>
       <c r="I60" t="s">
+        <v>28</v>
+      </c>
+      <c r="J60" t="s">
+        <v>29</v>
+      </c>
+      <c r="K60" t="s">
         <v>154</v>
-      </c>
-      <c r="J60" t="s">
-        <v>155</v>
-      </c>
-      <c r="K60" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B61">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D61">
-        <v>8100</v>
+        <v>8102</v>
       </c>
       <c r="E61" t="s">
         <v>152</v>
       </c>
       <c r="F61" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G61" s="2">
-        <v>-0.6</v>
+        <v>3.7280118318298694</v>
       </c>
       <c r="H61" s="2">
-        <v>3.8</v>
+        <v>-2.6318615669376433</v>
       </c>
       <c r="I61" t="s">
+        <v>28</v>
+      </c>
+      <c r="J61" t="s">
+        <v>29</v>
+      </c>
+      <c r="K61" t="s">
         <v>154</v>
-      </c>
-      <c r="J61" t="s">
-        <v>155</v>
-      </c>
-      <c r="K61" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B62">
         <v>2025</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D62">
-        <v>8101</v>
+        <v>8103</v>
       </c>
       <c r="E62" t="s">
         <v>152</v>
       </c>
       <c r="F62" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G62" s="2">
-        <v>0.3</v>
+        <v>7.0526353363169925</v>
       </c>
       <c r="H62" s="2">
-        <v>-3.5</v>
+        <v>1.4024298836386562</v>
       </c>
       <c r="I62" t="s">
+        <v>28</v>
+      </c>
+      <c r="J62" t="s">
+        <v>29</v>
+      </c>
+      <c r="K62" t="s">
         <v>154</v>
-      </c>
-      <c r="J62" t="s">
-        <v>155</v>
-      </c>
-      <c r="K62" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B63">
         <v>2025</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D63">
-        <v>8102</v>
+        <v>8104</v>
       </c>
       <c r="E63" t="s">
         <v>152</v>
       </c>
       <c r="F63" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G63" s="2">
-        <v>2.2999999999999998</v>
+        <v>5.1485330764510007</v>
       </c>
       <c r="H63" s="2">
-        <v>1.6</v>
+        <v>3.5961171450673124</v>
       </c>
       <c r="I63" t="s">
+        <v>28</v>
+      </c>
+      <c r="J63" t="s">
+        <v>29</v>
+      </c>
+      <c r="K63" t="s">
         <v>154</v>
-      </c>
-      <c r="J63" t="s">
-        <v>155</v>
-      </c>
-      <c r="K63" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B64">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>8103</v>
+        <v>8105</v>
       </c>
       <c r="E64" t="s">
         <v>152</v>
       </c>
       <c r="F64" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G64" s="2">
-        <v>1.4</v>
+        <v>2.1952446874675902</v>
       </c>
       <c r="H64" s="2">
-        <v>-0.4</v>
+        <v>-8.7004247706135018E-2</v>
       </c>
       <c r="I64" t="s">
+        <v>28</v>
+      </c>
+      <c r="J64" t="s">
+        <v>29</v>
+      </c>
+      <c r="K64" t="s">
         <v>154</v>
-      </c>
-      <c r="J64" t="s">
-        <v>155</v>
-      </c>
-      <c r="K64" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B65">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>8104</v>
+        <v>8097</v>
       </c>
       <c r="E65" t="s">
         <v>152</v>
       </c>
       <c r="F65" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G65" s="2">
-        <v>3.1</v>
+        <v>-1.4899625157390739</v>
       </c>
       <c r="H65" s="2">
-        <v>5.5</v>
+        <v>-10.120201144011299</v>
       </c>
       <c r="I65" t="s">
+        <v>28</v>
+      </c>
+      <c r="J65" t="s">
+        <v>29</v>
+      </c>
+      <c r="K65" t="s">
         <v>154</v>
-      </c>
-      <c r="J65" t="s">
-        <v>155</v>
-      </c>
-      <c r="K65" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B66">
         <v>2024</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66">
-        <v>8097</v>
+        <v>8098</v>
       </c>
       <c r="E66" t="s">
         <v>152</v>
       </c>
       <c r="F66" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G66" s="2">
-        <v>-2.2000000000000002</v>
+        <v>-3.3004128862410664</v>
       </c>
       <c r="H66" s="2">
-        <v>-5.0999999999999996</v>
+        <v>7.3363142594938369</v>
       </c>
       <c r="I66" t="s">
+        <v>28</v>
+      </c>
+      <c r="J66" t="s">
+        <v>29</v>
+      </c>
+      <c r="K66" t="s">
         <v>154</v>
-      </c>
-      <c r="J66" t="s">
-        <v>155</v>
-      </c>
-      <c r="K66" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B67">
         <v>2024</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67">
-        <v>8098</v>
+        <v>8099</v>
       </c>
       <c r="E67" t="s">
         <v>152</v>
       </c>
       <c r="F67" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G67" s="2">
-        <v>-3.7</v>
+        <v>8.4777238606219996</v>
       </c>
       <c r="H67" s="2">
-        <v>-0.6</v>
+        <v>1.5215467011807426</v>
       </c>
       <c r="I67" t="s">
+        <v>28</v>
+      </c>
+      <c r="J67" t="s">
+        <v>29</v>
+      </c>
+      <c r="K67" t="s">
         <v>154</v>
-      </c>
-      <c r="J67" t="s">
-        <v>155</v>
-      </c>
-      <c r="K67" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B68">
         <v>2024</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D68">
-        <v>8099</v>
+        <v>8100</v>
       </c>
       <c r="E68" t="s">
         <v>152</v>
       </c>
       <c r="F68" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G68" s="2">
-        <v>0.3</v>
+        <v>-2.0040025754278878</v>
       </c>
       <c r="H68" s="2">
-        <v>3.1</v>
+        <v>5.5586442646937684E-2</v>
       </c>
       <c r="I68" t="s">
+        <v>28</v>
+      </c>
+      <c r="J68" t="s">
+        <v>29</v>
+      </c>
+      <c r="K68" t="s">
         <v>154</v>
-      </c>
-      <c r="J68" t="s">
-        <v>155</v>
-      </c>
-      <c r="K68" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B69">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C69">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D69">
-        <v>8100</v>
+        <v>8101</v>
       </c>
       <c r="E69" t="s">
         <v>152</v>
       </c>
       <c r="F69" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G69" s="2">
-        <v>-1.5</v>
+        <v>4.7098020544573904</v>
       </c>
       <c r="H69" s="2">
-        <v>1.3</v>
+        <v>-3.9624454646840834</v>
       </c>
       <c r="I69" t="s">
+        <v>28</v>
+      </c>
+      <c r="J69" t="s">
+        <v>29</v>
+      </c>
+      <c r="K69" t="s">
         <v>154</v>
-      </c>
-      <c r="J69" t="s">
-        <v>155</v>
-      </c>
-      <c r="K69" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B70">
         <v>2025</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70">
-        <v>8101</v>
+        <v>8102</v>
       </c>
       <c r="E70" t="s">
         <v>152</v>
       </c>
       <c r="F70" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G70" s="2">
-        <v>2.2999999999999998</v>
+        <v>3.0114709531335437</v>
       </c>
       <c r="H70" s="2">
-        <v>-1.4</v>
+        <v>5.5953826825860586</v>
       </c>
       <c r="I70" t="s">
+        <v>28</v>
+      </c>
+      <c r="J70" t="s">
+        <v>29</v>
+      </c>
+      <c r="K70" t="s">
         <v>154</v>
-      </c>
-      <c r="J70" t="s">
-        <v>155</v>
-      </c>
-      <c r="K70" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B71">
         <v>2025</v>
       </c>
       <c r="C71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D71">
-        <v>8102</v>
+        <v>8103</v>
       </c>
       <c r="E71" t="s">
         <v>152</v>
       </c>
       <c r="F71" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G71" s="2">
-        <v>5.6</v>
+        <v>2.8757343000668012</v>
       </c>
       <c r="H71" s="2">
-        <v>2.5</v>
+        <v>1.3877732987055191</v>
       </c>
       <c r="I71" t="s">
+        <v>28</v>
+      </c>
+      <c r="J71" t="s">
+        <v>29</v>
+      </c>
+      <c r="K71" t="s">
         <v>154</v>
-      </c>
-      <c r="J71" t="s">
-        <v>155</v>
-      </c>
-      <c r="K71" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B72">
         <v>2025</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D72">
-        <v>8103</v>
+        <v>8104</v>
       </c>
       <c r="E72" t="s">
         <v>152</v>
       </c>
       <c r="F72" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G72" s="2">
-        <v>2.4</v>
+        <v>5.0665900429282651</v>
       </c>
       <c r="H72" s="2">
-        <v>0.1</v>
+        <v>2.1863839300686694</v>
       </c>
       <c r="I72" t="s">
+        <v>28</v>
+      </c>
+      <c r="J72" t="s">
+        <v>29</v>
+      </c>
+      <c r="K72" t="s">
         <v>154</v>
-      </c>
-      <c r="J72" t="s">
-        <v>155</v>
-      </c>
-      <c r="K72" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B73">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D73">
-        <v>8104</v>
+        <v>8105</v>
       </c>
       <c r="E73" t="s">
         <v>152</v>
       </c>
       <c r="F73" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G73" s="2">
-        <v>3</v>
+        <v>11.798814672517022</v>
       </c>
       <c r="H73" s="2">
-        <v>1.8</v>
+        <v>2.1912365929896094</v>
       </c>
       <c r="I73" t="s">
+        <v>28</v>
+      </c>
+      <c r="J73" t="s">
+        <v>29</v>
+      </c>
+      <c r="K73" t="s">
         <v>154</v>
-      </c>
-      <c r="J73" t="s">
-        <v>155</v>
-      </c>
-      <c r="K73" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -31167,22 +31260,22 @@
         <v>152</v>
       </c>
       <c r="F74" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G74" s="2">
-        <v>-9.9</v>
+        <v>1.5583565074475558</v>
       </c>
       <c r="H74" s="2">
-        <v>5.9</v>
+        <v>-0.13167344323491426</v>
       </c>
       <c r="I74" t="s">
+        <v>28</v>
+      </c>
+      <c r="J74" t="s">
+        <v>29</v>
+      </c>
+      <c r="K74" t="s">
         <v>154</v>
-      </c>
-      <c r="J74" t="s">
-        <v>155</v>
-      </c>
-      <c r="K74" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -31202,22 +31295,22 @@
         <v>152</v>
       </c>
       <c r="F75" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G75" s="2">
-        <v>-15.7</v>
+        <v>0.63724611093050054</v>
       </c>
       <c r="H75" s="2">
-        <v>-10.7</v>
+        <v>-2.6673658426257241E-2</v>
       </c>
       <c r="I75" t="s">
+        <v>28</v>
+      </c>
+      <c r="J75" t="s">
+        <v>29</v>
+      </c>
+      <c r="K75" t="s">
         <v>154</v>
-      </c>
-      <c r="J75" t="s">
-        <v>155</v>
-      </c>
-      <c r="K75" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -31237,22 +31330,22 @@
         <v>152</v>
       </c>
       <c r="F76" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G76" s="2">
-        <v>-2.6</v>
+        <v>0.85222904171189384</v>
       </c>
       <c r="H76" s="2">
-        <v>2.9</v>
+        <v>0.56706795442873492</v>
       </c>
       <c r="I76" t="s">
+        <v>28</v>
+      </c>
+      <c r="J76" t="s">
+        <v>29</v>
+      </c>
+      <c r="K76" t="s">
         <v>154</v>
-      </c>
-      <c r="J76" t="s">
-        <v>155</v>
-      </c>
-      <c r="K76" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -31272,22 +31365,22 @@
         <v>152</v>
       </c>
       <c r="F77" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G77" s="2">
-        <v>-2</v>
+        <v>0.12637724218769186</v>
       </c>
       <c r="H77" s="2">
-        <v>0.8</v>
+        <v>-0.28033761613766028</v>
       </c>
       <c r="I77" t="s">
+        <v>28</v>
+      </c>
+      <c r="J77" t="s">
+        <v>29</v>
+      </c>
+      <c r="K77" t="s">
         <v>154</v>
-      </c>
-      <c r="J77" t="s">
-        <v>155</v>
-      </c>
-      <c r="K77" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -31307,22 +31400,22 @@
         <v>152</v>
       </c>
       <c r="F78" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G78" s="2">
-        <v>1.9</v>
+        <v>0.33110676655236926</v>
       </c>
       <c r="H78" s="2">
-        <v>10</v>
+        <v>7.252844200464903E-2</v>
       </c>
       <c r="I78" t="s">
+        <v>28</v>
+      </c>
+      <c r="J78" t="s">
+        <v>29</v>
+      </c>
+      <c r="K78" t="s">
         <v>154</v>
-      </c>
-      <c r="J78" t="s">
-        <v>155</v>
-      </c>
-      <c r="K78" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -31342,22 +31435,22 @@
         <v>152</v>
       </c>
       <c r="F79" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G79" s="2">
-        <v>5.6</v>
+        <v>0.39262181726296141</v>
       </c>
       <c r="H79" s="2">
-        <v>-7.4</v>
+        <v>3.4622029798514475E-2</v>
       </c>
       <c r="I79" t="s">
+        <v>28</v>
+      </c>
+      <c r="J79" t="s">
+        <v>29</v>
+      </c>
+      <c r="K79" t="s">
         <v>154</v>
-      </c>
-      <c r="J79" t="s">
-        <v>155</v>
-      </c>
-      <c r="K79" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -31377,22 +31470,22 @@
         <v>152</v>
       </c>
       <c r="F80" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G80" s="2">
-        <v>2.7</v>
+        <v>-8.5845349516289193E-2</v>
       </c>
       <c r="H80" s="2">
-        <v>0.1</v>
+        <v>8.7769384429847719E-2</v>
       </c>
       <c r="I80" t="s">
+        <v>28</v>
+      </c>
+      <c r="J80" t="s">
+        <v>29</v>
+      </c>
+      <c r="K80" t="s">
         <v>154</v>
-      </c>
-      <c r="J80" t="s">
-        <v>155</v>
-      </c>
-      <c r="K80" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -31412,2262 +31505,2262 @@
         <v>152</v>
       </c>
       <c r="F81" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G81" s="2">
-        <v>0.8</v>
+        <v>0.45162830823886058</v>
       </c>
       <c r="H81" s="2">
-        <v>-1.1000000000000001</v>
+        <v>0.25608979876721172</v>
       </c>
       <c r="I81" t="s">
+        <v>28</v>
+      </c>
+      <c r="J81" t="s">
+        <v>29</v>
+      </c>
+      <c r="K81" t="s">
         <v>154</v>
-      </c>
-      <c r="J81" t="s">
-        <v>155</v>
-      </c>
-      <c r="K81" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B82">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C82">
         <v>1</v>
       </c>
       <c r="D82">
-        <v>8097</v>
+        <v>8105</v>
       </c>
       <c r="E82" t="s">
         <v>152</v>
       </c>
       <c r="F82" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G82" s="2">
-        <v>1.6</v>
+        <v>0.10115829220276318</v>
       </c>
       <c r="H82" s="2">
-        <v>-0.1</v>
+        <v>-0.27661891616681533</v>
       </c>
       <c r="I82" t="s">
+        <v>28</v>
+      </c>
+      <c r="J82" t="s">
+        <v>29</v>
+      </c>
+      <c r="K82" t="s">
         <v>154</v>
-      </c>
-      <c r="J82" t="s">
-        <v>155</v>
-      </c>
-      <c r="K82" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B83">
         <v>2024</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D83">
-        <v>8098</v>
+        <v>8097</v>
       </c>
       <c r="E83" t="s">
         <v>152</v>
       </c>
       <c r="F83" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G83" s="2">
-        <v>0.6</v>
+        <v>-2.5115267847079514</v>
       </c>
       <c r="H83" s="2">
-        <v>0</v>
+        <v>-4.3886793501873855</v>
       </c>
       <c r="I83" t="s">
+        <v>28</v>
+      </c>
+      <c r="J83" t="s">
+        <v>29</v>
+      </c>
+      <c r="K83" t="s">
         <v>154</v>
-      </c>
-      <c r="J83" t="s">
-        <v>155</v>
-      </c>
-      <c r="K83" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B84">
         <v>2024</v>
       </c>
       <c r="C84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D84">
-        <v>8099</v>
+        <v>8098</v>
       </c>
       <c r="E84" t="s">
         <v>152</v>
       </c>
       <c r="F84" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G84" s="2">
-        <v>0.9</v>
+        <v>-6.6274108383136525</v>
       </c>
       <c r="H84" s="2">
-        <v>0.6</v>
+        <v>-0.37743015124794832</v>
       </c>
       <c r="I84" t="s">
+        <v>28</v>
+      </c>
+      <c r="J84" t="s">
+        <v>29</v>
+      </c>
+      <c r="K84" t="s">
         <v>154</v>
-      </c>
-      <c r="J84" t="s">
-        <v>155</v>
-      </c>
-      <c r="K84" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B85">
         <v>2024</v>
       </c>
       <c r="C85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D85">
-        <v>8100</v>
+        <v>8099</v>
       </c>
       <c r="E85" t="s">
         <v>152</v>
       </c>
       <c r="F85" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G85" s="2">
-        <v>0.1</v>
+        <v>-2.7047034345200061</v>
       </c>
       <c r="H85" s="2">
-        <v>-0.3</v>
+        <v>0.55787042622634786</v>
       </c>
       <c r="I85" t="s">
+        <v>28</v>
+      </c>
+      <c r="J85" t="s">
+        <v>29</v>
+      </c>
+      <c r="K85" t="s">
         <v>154</v>
-      </c>
-      <c r="J85" t="s">
-        <v>155</v>
-      </c>
-      <c r="K85" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B86">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D86">
-        <v>8101</v>
+        <v>8100</v>
       </c>
       <c r="E86" t="s">
         <v>152</v>
       </c>
       <c r="F86" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G86" s="2">
-        <v>0.3</v>
+        <v>-0.60281449453802871</v>
       </c>
       <c r="H86" s="2">
-        <v>0.1</v>
+        <v>3.7745747130764284</v>
       </c>
       <c r="I86" t="s">
+        <v>28</v>
+      </c>
+      <c r="J86" t="s">
+        <v>29</v>
+      </c>
+      <c r="K86" t="s">
         <v>154</v>
-      </c>
-      <c r="J86" t="s">
-        <v>155</v>
-      </c>
-      <c r="K86" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B87">
         <v>2025</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87">
-        <v>8102</v>
+        <v>8101</v>
       </c>
       <c r="E87" t="s">
         <v>152</v>
       </c>
       <c r="F87" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G87" s="2">
-        <v>0.4</v>
+        <v>0.31328058654207513</v>
       </c>
       <c r="H87" s="2">
-        <v>0</v>
+        <v>-3.5074767276236596</v>
       </c>
       <c r="I87" t="s">
+        <v>28</v>
+      </c>
+      <c r="J87" t="s">
+        <v>29</v>
+      </c>
+      <c r="K87" t="s">
         <v>154</v>
-      </c>
-      <c r="J87" t="s">
-        <v>155</v>
-      </c>
-      <c r="K87" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B88">
         <v>2025</v>
       </c>
       <c r="C88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D88">
-        <v>8103</v>
+        <v>8102</v>
       </c>
       <c r="E88" t="s">
         <v>152</v>
       </c>
       <c r="F88" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G88" s="2">
-        <v>-0.1</v>
+        <v>2.3178884162770697</v>
       </c>
       <c r="H88" s="2">
-        <v>0.1</v>
+        <v>1.613374878449414</v>
       </c>
       <c r="I88" t="s">
+        <v>28</v>
+      </c>
+      <c r="J88" t="s">
+        <v>29</v>
+      </c>
+      <c r="K88" t="s">
         <v>154</v>
-      </c>
-      <c r="J88" t="s">
-        <v>155</v>
-      </c>
-      <c r="K88" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B89">
         <v>2025</v>
       </c>
       <c r="C89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D89">
-        <v>8104</v>
+        <v>8103</v>
       </c>
       <c r="E89" t="s">
         <v>152</v>
       </c>
       <c r="F89" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G89" s="2">
-        <v>0.5</v>
+        <v>1.3552925031841356</v>
       </c>
       <c r="H89" s="2">
-        <v>0.3</v>
+        <v>-0.38816742306743146</v>
       </c>
       <c r="I89" t="s">
+        <v>28</v>
+      </c>
+      <c r="J89" t="s">
+        <v>29</v>
+      </c>
+      <c r="K89" t="s">
         <v>154</v>
-      </c>
-      <c r="J89" t="s">
-        <v>155</v>
-      </c>
-      <c r="K89" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B90">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D90">
-        <v>8097</v>
+        <v>8104</v>
       </c>
       <c r="E90" t="s">
         <v>152</v>
       </c>
       <c r="F90" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G90" s="2">
-        <v>-8.1999999999999993</v>
+        <v>3.0797131162970004</v>
       </c>
       <c r="H90" s="2">
-        <v>5.3</v>
+        <v>5.5401560787128545</v>
       </c>
       <c r="I90" t="s">
+        <v>28</v>
+      </c>
+      <c r="J90" t="s">
+        <v>29</v>
+      </c>
+      <c r="K90" t="s">
         <v>154</v>
-      </c>
-      <c r="J90" t="s">
-        <v>155</v>
-      </c>
-      <c r="K90" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B91">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91">
-        <v>8098</v>
+        <v>8105</v>
       </c>
       <c r="E91" t="s">
         <v>152</v>
       </c>
       <c r="F91" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G91" s="2">
-        <v>3.2</v>
+        <v>0.61713074506526411</v>
       </c>
       <c r="H91" s="2">
-        <v>-0.7</v>
+        <v>-5.8126906206632523</v>
       </c>
       <c r="I91" t="s">
+        <v>28</v>
+      </c>
+      <c r="J91" t="s">
+        <v>29</v>
+      </c>
+      <c r="K91" t="s">
         <v>154</v>
-      </c>
-      <c r="J91" t="s">
-        <v>155</v>
-      </c>
-      <c r="K91" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B92">
         <v>2024</v>
       </c>
       <c r="C92">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D92">
-        <v>8099</v>
+        <v>8097</v>
       </c>
       <c r="E92" t="s">
         <v>152</v>
       </c>
       <c r="F92" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G92" s="2">
-        <v>-2.2000000000000002</v>
+        <v>-8.19316906298676</v>
       </c>
       <c r="H92" s="2">
-        <v>-1.6</v>
+        <v>5.2579642123795178</v>
       </c>
       <c r="I92" t="s">
+        <v>28</v>
+      </c>
+      <c r="J92" t="s">
+        <v>29</v>
+      </c>
+      <c r="K92" t="s">
         <v>154</v>
-      </c>
-      <c r="J92" t="s">
-        <v>155</v>
-      </c>
-      <c r="K92" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B93">
         <v>2024</v>
       </c>
       <c r="C93">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D93">
-        <v>8100</v>
+        <v>8098</v>
       </c>
       <c r="E93" t="s">
         <v>152</v>
       </c>
       <c r="F93" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G93" s="2">
-        <v>4.0999999999999996</v>
+        <v>3.1976766222678865</v>
       </c>
       <c r="H93" s="2">
-        <v>1.2</v>
+        <v>-0.72433615970061149</v>
       </c>
       <c r="I93" t="s">
+        <v>28</v>
+      </c>
+      <c r="J93" t="s">
+        <v>29</v>
+      </c>
+      <c r="K93" t="s">
         <v>154</v>
-      </c>
-      <c r="J93" t="s">
-        <v>155</v>
-      </c>
-      <c r="K93" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B94">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D94">
-        <v>8101</v>
+        <v>8099</v>
       </c>
       <c r="E94" t="s">
         <v>152</v>
       </c>
       <c r="F94" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G94" s="2">
-        <v>12.4</v>
+        <v>-2.1582616139177668</v>
       </c>
       <c r="H94" s="2">
-        <v>13.7</v>
+        <v>-1.5521669063886745</v>
       </c>
       <c r="I94" t="s">
+        <v>28</v>
+      </c>
+      <c r="J94" t="s">
+        <v>29</v>
+      </c>
+      <c r="K94" t="s">
         <v>154</v>
-      </c>
-      <c r="J94" t="s">
-        <v>155</v>
-      </c>
-      <c r="K94" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B95">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C95">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D95">
-        <v>8102</v>
+        <v>8100</v>
       </c>
       <c r="E95" t="s">
         <v>152</v>
       </c>
       <c r="F95" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G95" s="2">
-        <v>15</v>
+        <v>4.0681522312902452</v>
       </c>
       <c r="H95" s="2">
-        <v>1.5</v>
+        <v>1.1611869095479399</v>
       </c>
       <c r="I95" t="s">
+        <v>28</v>
+      </c>
+      <c r="J95" t="s">
+        <v>29</v>
+      </c>
+      <c r="K95" t="s">
         <v>154</v>
-      </c>
-      <c r="J95" t="s">
-        <v>155</v>
-      </c>
-      <c r="K95" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B96">
         <v>2025</v>
       </c>
       <c r="C96">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D96">
-        <v>8103</v>
+        <v>8101</v>
       </c>
       <c r="E96" t="s">
         <v>152</v>
       </c>
       <c r="F96" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G96" s="2">
-        <v>12.2</v>
+        <v>12.448058812497242</v>
       </c>
       <c r="H96" s="2">
-        <v>-3.9</v>
+        <v>13.733678329676625</v>
       </c>
       <c r="I96" t="s">
+        <v>28</v>
+      </c>
+      <c r="J96" t="s">
+        <v>29</v>
+      </c>
+      <c r="K96" t="s">
         <v>154</v>
-      </c>
-      <c r="J96" t="s">
-        <v>155</v>
-      </c>
-      <c r="K96" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B97">
         <v>2025</v>
       </c>
       <c r="C97">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D97">
-        <v>8104</v>
+        <v>8102</v>
       </c>
       <c r="E97" t="s">
         <v>152</v>
       </c>
       <c r="F97" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G97" s="2">
-        <v>0.4</v>
+        <v>15.011970015174425</v>
       </c>
       <c r="H97" s="2">
-        <v>-9.6</v>
+        <v>1.5392332550260734</v>
       </c>
       <c r="I97" t="s">
+        <v>28</v>
+      </c>
+      <c r="J97" t="s">
+        <v>29</v>
+      </c>
+      <c r="K97" t="s">
         <v>154</v>
-      </c>
-      <c r="J97" t="s">
-        <v>155</v>
-      </c>
-      <c r="K97" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B98">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D98">
-        <v>8097</v>
+        <v>8103</v>
       </c>
       <c r="E98" t="s">
         <v>152</v>
       </c>
       <c r="F98" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G98" s="2">
-        <v>4.9000000000000004</v>
+        <v>12.242973292667326</v>
       </c>
       <c r="H98" s="2">
-        <v>0.4</v>
+        <v>-3.9223700003637507</v>
       </c>
       <c r="I98" t="s">
+        <v>28</v>
+      </c>
+      <c r="J98" t="s">
+        <v>29</v>
+      </c>
+      <c r="K98" t="s">
         <v>154</v>
-      </c>
-      <c r="J98" t="s">
-        <v>155</v>
-      </c>
-      <c r="K98" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B99">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C99">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D99">
-        <v>8098</v>
+        <v>8104</v>
       </c>
       <c r="E99" t="s">
         <v>152</v>
       </c>
       <c r="F99" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G99" s="2">
-        <v>3.2</v>
+        <v>0.35187663669509206</v>
       </c>
       <c r="H99" s="2">
-        <v>0.3</v>
+        <v>-9.5558977870394131</v>
       </c>
       <c r="I99" t="s">
+        <v>28</v>
+      </c>
+      <c r="J99" t="s">
+        <v>29</v>
+      </c>
+      <c r="K99" t="s">
         <v>154</v>
-      </c>
-      <c r="J99" t="s">
-        <v>155</v>
-      </c>
-      <c r="K99" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B100">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D100">
-        <v>8099</v>
+        <v>8105</v>
       </c>
       <c r="E100" t="s">
         <v>152</v>
       </c>
       <c r="F100" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G100" s="2">
-        <v>1.4</v>
+        <v>1.7993799474574024</v>
       </c>
       <c r="H100" s="2">
-        <v>-0.2</v>
+        <v>15.374204460776241</v>
       </c>
       <c r="I100" t="s">
+        <v>28</v>
+      </c>
+      <c r="J100" t="s">
+        <v>29</v>
+      </c>
+      <c r="K100" t="s">
         <v>154</v>
-      </c>
-      <c r="J100" t="s">
-        <v>155</v>
-      </c>
-      <c r="K100" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B101">
         <v>2024</v>
       </c>
       <c r="C101">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D101">
-        <v>8100</v>
+        <v>8097</v>
       </c>
       <c r="E101" t="s">
         <v>152</v>
       </c>
       <c r="F101" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G101" s="2">
-        <v>-0.1</v>
+        <v>4.8509376571331586</v>
       </c>
       <c r="H101" s="2">
-        <v>-0.6</v>
+        <v>0.38736240145000878</v>
       </c>
       <c r="I101" t="s">
+        <v>28</v>
+      </c>
+      <c r="J101" t="s">
+        <v>29</v>
+      </c>
+      <c r="K101" t="s">
         <v>154</v>
-      </c>
-      <c r="J101" t="s">
-        <v>155</v>
-      </c>
-      <c r="K101" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B102">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D102">
-        <v>8101</v>
+        <v>8098</v>
       </c>
       <c r="E102" t="s">
         <v>152</v>
       </c>
       <c r="F102" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G102" s="2">
-        <v>-1.7</v>
+        <v>3.1754685959306528</v>
       </c>
       <c r="H102" s="2">
-        <v>-1.2</v>
+        <v>0.31895538815949198</v>
       </c>
       <c r="I102" t="s">
+        <v>28</v>
+      </c>
+      <c r="J102" t="s">
+        <v>29</v>
+      </c>
+      <c r="K102" t="s">
         <v>154</v>
-      </c>
-      <c r="J102" t="s">
-        <v>155</v>
-      </c>
-      <c r="K102" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B103">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C103">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D103">
-        <v>8102</v>
+        <v>8099</v>
       </c>
       <c r="E103" t="s">
         <v>152</v>
       </c>
       <c r="F103" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G103" s="2">
-        <v>-2.9</v>
+        <v>1.4468587226099894</v>
       </c>
       <c r="H103" s="2">
-        <v>-0.9</v>
+        <v>-0.23229570507657948</v>
       </c>
       <c r="I103" t="s">
+        <v>28</v>
+      </c>
+      <c r="J103" t="s">
+        <v>29</v>
+      </c>
+      <c r="K103" t="s">
         <v>154</v>
-      </c>
-      <c r="J103" t="s">
-        <v>155</v>
-      </c>
-      <c r="K103" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B104">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C104">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D104">
-        <v>8103</v>
+        <v>8100</v>
       </c>
       <c r="E104" t="s">
         <v>152</v>
       </c>
       <c r="F104" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G104" s="2">
-        <v>-3.8</v>
+        <v>-0.14866061807162767</v>
       </c>
       <c r="H104" s="2">
-        <v>-1.2</v>
+        <v>-0.61934131286889293</v>
       </c>
       <c r="I104" t="s">
+        <v>28</v>
+      </c>
+      <c r="J104" t="s">
+        <v>29</v>
+      </c>
+      <c r="K104" t="s">
         <v>154</v>
-      </c>
-      <c r="J104" t="s">
-        <v>155</v>
-      </c>
-      <c r="K104" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B105">
         <v>2025</v>
       </c>
       <c r="C105">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D105">
-        <v>8104</v>
+        <v>8101</v>
       </c>
       <c r="E105" t="s">
         <v>152</v>
       </c>
       <c r="F105" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G105" s="2">
-        <v>-4.3</v>
+        <v>-1.7227432413192245</v>
       </c>
       <c r="H105" s="2">
-        <v>-1.1000000000000001</v>
+        <v>-1.1951702288371724</v>
       </c>
       <c r="I105" t="s">
+        <v>28</v>
+      </c>
+      <c r="J105" t="s">
+        <v>29</v>
+      </c>
+      <c r="K105" t="s">
         <v>154</v>
-      </c>
-      <c r="J105" t="s">
-        <v>155</v>
-      </c>
-      <c r="K105" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B106">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106">
-        <v>8097</v>
+        <v>8102</v>
       </c>
       <c r="E106" t="s">
         <v>152</v>
       </c>
       <c r="F106" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G106" s="2">
-        <v>-3.1</v>
+        <v>-2.8805231721465652</v>
       </c>
       <c r="H106" s="2">
-        <v>-3.3</v>
+        <v>-0.86287728666956109</v>
       </c>
       <c r="I106" t="s">
+        <v>28</v>
+      </c>
+      <c r="J106" t="s">
+        <v>29</v>
+      </c>
+      <c r="K106" t="s">
         <v>154</v>
-      </c>
-      <c r="J106" t="s">
-        <v>155</v>
-      </c>
-      <c r="K106" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="107" spans="1:11">
       <c r="A107" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B107">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C107">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D107">
-        <v>8098</v>
+        <v>8103</v>
       </c>
       <c r="E107" t="s">
         <v>152</v>
       </c>
       <c r="F107" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G107" s="2">
-        <v>-9.3000000000000007</v>
+        <v>-3.8270263568905838</v>
       </c>
       <c r="H107" s="2">
-        <v>-0.7</v>
+        <v>-1.2046078811102867</v>
       </c>
       <c r="I107" t="s">
+        <v>28</v>
+      </c>
+      <c r="J107" t="s">
+        <v>29</v>
+      </c>
+      <c r="K107" t="s">
         <v>154</v>
-      </c>
-      <c r="J107" t="s">
-        <v>155</v>
-      </c>
-      <c r="K107" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B108">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C108">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D108">
-        <v>8099</v>
+        <v>8104</v>
       </c>
       <c r="E108" t="s">
         <v>152</v>
       </c>
       <c r="F108" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G108" s="2">
-        <v>4</v>
+        <v>-4.2646380311792909</v>
       </c>
       <c r="H108" s="2">
-        <v>4.7</v>
+        <v>-1.0715487760734499</v>
       </c>
       <c r="I108" t="s">
+        <v>28</v>
+      </c>
+      <c r="J108" t="s">
+        <v>29</v>
+      </c>
+      <c r="K108" t="s">
         <v>154</v>
-      </c>
-      <c r="J108" t="s">
-        <v>155</v>
-      </c>
-      <c r="K108" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B109">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C109">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D109">
-        <v>8100</v>
+        <v>8105</v>
       </c>
       <c r="E109" t="s">
         <v>152</v>
       </c>
       <c r="F109" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G109" s="2">
-        <v>-1.2</v>
+        <v>-4.3373186902438077</v>
       </c>
       <c r="H109" s="2">
-        <v>-1.9</v>
+        <v>-1.2701811756685388</v>
       </c>
       <c r="I109" t="s">
+        <v>28</v>
+      </c>
+      <c r="J109" t="s">
+        <v>29</v>
+      </c>
+      <c r="K109" t="s">
         <v>154</v>
-      </c>
-      <c r="J109" t="s">
-        <v>155</v>
-      </c>
-      <c r="K109" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B110">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C110">
         <v>1</v>
       </c>
       <c r="D110">
-        <v>8101</v>
+        <v>8097</v>
       </c>
       <c r="E110" t="s">
         <v>152</v>
       </c>
       <c r="F110" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G110" s="2">
-        <v>11.7</v>
+        <v>-9.9383491979470833</v>
       </c>
       <c r="H110" s="2">
-        <v>9.4</v>
+        <v>5.8885596959186159</v>
       </c>
       <c r="I110" t="s">
+        <v>28</v>
+      </c>
+      <c r="J110" t="s">
+        <v>29</v>
+      </c>
+      <c r="K110" t="s">
         <v>154</v>
-      </c>
-      <c r="J110" t="s">
-        <v>155</v>
-      </c>
-      <c r="K110" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="111" spans="1:11">
       <c r="A111" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B111">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C111">
         <v>2</v>
       </c>
       <c r="D111">
-        <v>8102</v>
+        <v>8098</v>
       </c>
       <c r="E111" t="s">
         <v>152</v>
       </c>
       <c r="F111" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G111" s="2">
-        <v>4</v>
+        <v>-15.681479800116271</v>
       </c>
       <c r="H111" s="2">
-        <v>-7.5</v>
+        <v>-10.670523252440923</v>
       </c>
       <c r="I111" t="s">
+        <v>28</v>
+      </c>
+      <c r="J111" t="s">
+        <v>29</v>
+      </c>
+      <c r="K111" t="s">
         <v>154</v>
-      </c>
-      <c r="J111" t="s">
-        <v>155</v>
-      </c>
-      <c r="K111" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="112" spans="1:11">
       <c r="A112" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B112">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C112">
         <v>3</v>
       </c>
       <c r="D112">
-        <v>8103</v>
+        <v>8099</v>
       </c>
       <c r="E112" t="s">
         <v>152</v>
       </c>
       <c r="F112" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G112" s="2">
-        <v>-8</v>
+        <v>-2.6046978241620722</v>
       </c>
       <c r="H112" s="2">
-        <v>-7.3</v>
+        <v>2.875527462135552</v>
       </c>
       <c r="I112" t="s">
+        <v>28</v>
+      </c>
+      <c r="J112" t="s">
+        <v>29</v>
+      </c>
+      <c r="K112" t="s">
         <v>154</v>
-      </c>
-      <c r="J112" t="s">
-        <v>155</v>
-      </c>
-      <c r="K112" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="113" spans="1:11">
       <c r="A113" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B113">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C113">
         <v>4</v>
       </c>
       <c r="D113">
-        <v>8104</v>
+        <v>8100</v>
       </c>
       <c r="E113" t="s">
         <v>152</v>
       </c>
       <c r="F113" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G113" s="2">
-        <v>-9.6</v>
+        <v>-1.9555904552586378</v>
       </c>
       <c r="H113" s="2">
-        <v>-3.5</v>
+        <v>0.75507469871618493</v>
       </c>
       <c r="I113" t="s">
+        <v>28</v>
+      </c>
+      <c r="J113" t="s">
+        <v>29</v>
+      </c>
+      <c r="K113" t="s">
         <v>154</v>
-      </c>
-      <c r="J113" t="s">
-        <v>155</v>
-      </c>
-      <c r="K113" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="114" spans="1:11">
       <c r="A114" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B114">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C114">
         <v>1</v>
       </c>
       <c r="D114">
-        <v>8097</v>
+        <v>8101</v>
       </c>
       <c r="E114" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F114" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G114" s="2">
-        <v>4.9000000000000004</v>
+        <v>1.862879769066117</v>
       </c>
       <c r="H114" s="2">
-        <v>-3.1</v>
+        <v>10.012530804245689</v>
       </c>
       <c r="I114" t="s">
+        <v>28</v>
+      </c>
+      <c r="J114" t="s">
+        <v>29</v>
+      </c>
+      <c r="K114" t="s">
         <v>154</v>
-      </c>
-      <c r="J114" t="s">
-        <v>155</v>
-      </c>
-      <c r="K114" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="115" spans="1:11">
       <c r="A115" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B115">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C115">
         <v>2</v>
       </c>
       <c r="D115">
-        <v>8098</v>
+        <v>8102</v>
       </c>
       <c r="E115" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F115" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G115" s="2">
-        <v>-10.7</v>
+        <v>5.6265503394290262</v>
       </c>
       <c r="H115" s="2">
-        <v>-6.4</v>
+        <v>-7.3699418879348055</v>
       </c>
       <c r="I115" t="s">
+        <v>28</v>
+      </c>
+      <c r="J115" t="s">
+        <v>29</v>
+      </c>
+      <c r="K115" t="s">
         <v>154</v>
-      </c>
-      <c r="J115" t="s">
-        <v>155</v>
-      </c>
-      <c r="K115" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="116" spans="1:11">
       <c r="A116" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B116">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C116">
         <v>3</v>
       </c>
       <c r="D116">
-        <v>8099</v>
+        <v>8103</v>
       </c>
       <c r="E116" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F116" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G116" s="2">
-        <v>-18.5</v>
+        <v>2.7270444990249665</v>
       </c>
       <c r="H116" s="2">
-        <v>-8.1</v>
+        <v>5.1538685141827578E-2</v>
       </c>
       <c r="I116" t="s">
+        <v>28</v>
+      </c>
+      <c r="J116" t="s">
+        <v>29</v>
+      </c>
+      <c r="K116" t="s">
         <v>154</v>
-      </c>
-      <c r="J116" t="s">
-        <v>155</v>
-      </c>
-      <c r="K116" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="117" spans="1:11">
       <c r="A117" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B117">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C117">
         <v>4</v>
       </c>
       <c r="D117">
-        <v>8100</v>
+        <v>8104</v>
       </c>
       <c r="E117" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F117" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G117" s="2">
-        <v>-22.6</v>
+        <v>0.83407163481605817</v>
       </c>
       <c r="H117" s="2">
-        <v>-7.1</v>
+        <v>-1.1015602630520593</v>
       </c>
       <c r="I117" t="s">
+        <v>28</v>
+      </c>
+      <c r="J117" t="s">
+        <v>29</v>
+      </c>
+      <c r="K117" t="s">
         <v>154</v>
-      </c>
-      <c r="J117" t="s">
-        <v>155</v>
-      </c>
-      <c r="K117" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="118" spans="1:11">
       <c r="A118" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B118">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C118">
         <v>1</v>
       </c>
       <c r="D118">
-        <v>8101</v>
+        <v>8105</v>
       </c>
       <c r="E118" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F118" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G118" s="2">
-        <v>3.4</v>
+        <v>4.2221945954346918</v>
       </c>
       <c r="H118" s="2">
-        <v>29.5</v>
+        <v>13.709058927433482</v>
       </c>
       <c r="I118" t="s">
+        <v>28</v>
+      </c>
+      <c r="J118" t="s">
+        <v>29</v>
+      </c>
+      <c r="K118" t="s">
         <v>154</v>
-      </c>
-      <c r="J118" t="s">
-        <v>155</v>
-      </c>
-      <c r="K118" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="119" spans="1:11">
       <c r="A119" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B119">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D119">
-        <v>8102</v>
+        <v>8097</v>
       </c>
       <c r="E119" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F119" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G119" s="2">
-        <v>2.9</v>
+        <v>-3.1076205824418612</v>
       </c>
       <c r="H119" s="2">
-        <v>-6.9</v>
+        <v>-3.2933159796737277</v>
       </c>
       <c r="I119" t="s">
+        <v>28</v>
+      </c>
+      <c r="J119" t="s">
+        <v>29</v>
+      </c>
+      <c r="K119" t="s">
         <v>154</v>
-      </c>
-      <c r="J119" t="s">
-        <v>155</v>
-      </c>
-      <c r="K119" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="120" spans="1:11">
       <c r="A120" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B120">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C120">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D120">
-        <v>8103</v>
+        <v>8098</v>
       </c>
       <c r="E120" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F120" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G120" s="2">
-        <v>16.8</v>
+        <v>-9.2561766398208789</v>
       </c>
       <c r="H120" s="2">
-        <v>4.3</v>
+        <v>-0.66416411950839249</v>
       </c>
       <c r="I120" t="s">
+        <v>28</v>
+      </c>
+      <c r="J120" t="s">
+        <v>29</v>
+      </c>
+      <c r="K120" t="s">
         <v>154</v>
-      </c>
-      <c r="J120" t="s">
-        <v>155</v>
-      </c>
-      <c r="K120" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="121" spans="1:11">
       <c r="A121" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B121">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C121">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D121">
-        <v>8104</v>
+        <v>8099</v>
       </c>
       <c r="E121" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F121" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G121" s="2">
-        <v>32.700000000000003</v>
+        <v>4.0019591148555911</v>
       </c>
       <c r="H121" s="2">
-        <v>5.6</v>
+        <v>4.7407864547372114</v>
       </c>
       <c r="I121" t="s">
+        <v>28</v>
+      </c>
+      <c r="J121" t="s">
+        <v>29</v>
+      </c>
+      <c r="K121" t="s">
         <v>154</v>
-      </c>
-      <c r="J121" t="s">
-        <v>155</v>
-      </c>
-      <c r="K121" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="122" spans="1:11">
       <c r="A122" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B122">
         <v>2024</v>
       </c>
       <c r="C122">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D122">
-        <v>8097</v>
+        <v>8100</v>
       </c>
       <c r="E122" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F122" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G122" s="2">
-        <v>2.8</v>
+        <v>-1.2488667879971604</v>
       </c>
       <c r="H122" s="2">
-        <v>-1.3</v>
+        <v>-1.8559862961368134</v>
       </c>
       <c r="I122" t="s">
+        <v>28</v>
+      </c>
+      <c r="J122" t="s">
+        <v>29</v>
+      </c>
+      <c r="K122" t="s">
         <v>154</v>
-      </c>
-      <c r="J122" t="s">
-        <v>155</v>
-      </c>
-      <c r="K122" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="123" spans="1:11">
       <c r="A123" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B123">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D123">
-        <v>8098</v>
+        <v>8101</v>
       </c>
       <c r="E123" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F123" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G123" s="2">
-        <v>-0.5</v>
+        <v>11.70372199877081</v>
       </c>
       <c r="H123" s="2">
-        <v>-0.5</v>
+        <v>9.3911147737238743</v>
       </c>
       <c r="I123" t="s">
+        <v>28</v>
+      </c>
+      <c r="J123" t="s">
+        <v>29</v>
+      </c>
+      <c r="K123" t="s">
         <v>154</v>
-      </c>
-      <c r="J123" t="s">
-        <v>155</v>
-      </c>
-      <c r="K123" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="124" spans="1:11">
       <c r="A124" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B124">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C124">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D124">
-        <v>8099</v>
+        <v>8102</v>
       </c>
       <c r="E124" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F124" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G124" s="2">
-        <v>-1</v>
+        <v>3.9725851070458562</v>
       </c>
       <c r="H124" s="2">
-        <v>-0.1</v>
+        <v>-7.5393060727411925</v>
       </c>
       <c r="I124" t="s">
+        <v>28</v>
+      </c>
+      <c r="J124" t="s">
+        <v>29</v>
+      </c>
+      <c r="K124" t="s">
         <v>154</v>
-      </c>
-      <c r="J124" t="s">
-        <v>155</v>
-      </c>
-      <c r="K124" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="125" spans="1:11">
       <c r="A125" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B125">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D125">
-        <v>8100</v>
+        <v>8103</v>
       </c>
       <c r="E125" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F125" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G125" s="2">
-        <v>-2.6</v>
+        <v>-7.9866577071566418</v>
       </c>
       <c r="H125" s="2">
-        <v>-0.8</v>
+        <v>-7.306817213798011</v>
       </c>
       <c r="I125" t="s">
+        <v>28</v>
+      </c>
+      <c r="J125" t="s">
+        <v>29</v>
+      </c>
+      <c r="K125" t="s">
         <v>154</v>
-      </c>
-      <c r="J125" t="s">
-        <v>155</v>
-      </c>
-      <c r="K125" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="126" spans="1:11">
       <c r="A126" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B126">
         <v>2025</v>
       </c>
       <c r="C126">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D126">
-        <v>8101</v>
+        <v>8104</v>
       </c>
       <c r="E126" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F126" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G126" s="2">
-        <v>1.7</v>
+        <v>-9.5739152985602196</v>
       </c>
       <c r="H126" s="2">
-        <v>3.1</v>
+        <v>-3.5489997974449849</v>
       </c>
       <c r="I126" t="s">
+        <v>28</v>
+      </c>
+      <c r="J126" t="s">
+        <v>29</v>
+      </c>
+      <c r="K126" t="s">
         <v>154</v>
-      </c>
-      <c r="J126" t="s">
-        <v>155</v>
-      </c>
-      <c r="K126" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="127" spans="1:11">
       <c r="A127" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B127">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D127">
-        <v>8102</v>
+        <v>8105</v>
       </c>
       <c r="E127" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F127" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G127" s="2">
-        <v>3.7</v>
+        <v>-9.3810907530806116</v>
       </c>
       <c r="H127" s="2">
-        <v>1.6</v>
+        <v>9.6243803414568507</v>
       </c>
       <c r="I127" t="s">
+        <v>28</v>
+      </c>
+      <c r="J127" t="s">
+        <v>29</v>
+      </c>
+      <c r="K127" t="s">
         <v>154</v>
-      </c>
-      <c r="J127" t="s">
-        <v>155</v>
-      </c>
-      <c r="K127" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="128" spans="1:11">
       <c r="A128" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B128">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C128">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D128">
-        <v>8103</v>
+        <v>8097</v>
       </c>
       <c r="E128" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F128" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G128" s="2">
-        <v>4.0999999999999996</v>
+        <v>4.91887346100226</v>
       </c>
       <c r="H128" s="2">
-        <v>0.2</v>
+        <v>-3.1158476922358846</v>
       </c>
       <c r="I128" t="s">
+        <v>28</v>
+      </c>
+      <c r="J128" t="s">
+        <v>29</v>
+      </c>
+      <c r="K128" t="s">
         <v>154</v>
-      </c>
-      <c r="J128" t="s">
-        <v>155</v>
-      </c>
-      <c r="K128" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="129" spans="1:11">
       <c r="A129" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B129">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C129">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D129">
-        <v>8104</v>
+        <v>8098</v>
       </c>
       <c r="E129" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F129" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G129" s="2">
-        <v>5.0999999999999996</v>
+        <v>-10.740300762162336</v>
       </c>
       <c r="H129" s="2">
-        <v>0.2</v>
+        <v>-6.4277060431266353</v>
       </c>
       <c r="I129" t="s">
+        <v>28</v>
+      </c>
+      <c r="J129" t="s">
+        <v>29</v>
+      </c>
+      <c r="K129" t="s">
         <v>154</v>
-      </c>
-      <c r="J129" t="s">
-        <v>155</v>
-      </c>
-      <c r="K129" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="130" spans="1:11">
       <c r="A130" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B130">
         <v>2024</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D130">
-        <v>8097</v>
+        <v>8099</v>
       </c>
       <c r="E130" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F130" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G130" s="2">
-        <v>1.4</v>
+        <v>-18.506055760089701</v>
       </c>
       <c r="H130" s="2">
-        <v>-0.7</v>
+        <v>-8.1050577137981588</v>
       </c>
       <c r="I130" t="s">
+        <v>28</v>
+      </c>
+      <c r="J130" t="s">
+        <v>29</v>
+      </c>
+      <c r="K130" t="s">
         <v>154</v>
-      </c>
-      <c r="J130" t="s">
-        <v>155</v>
-      </c>
-      <c r="K130" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="131" spans="1:11">
       <c r="A131" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B131">
         <v>2024</v>
       </c>
       <c r="C131">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D131">
-        <v>8098</v>
+        <v>8100</v>
       </c>
       <c r="E131" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F131" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G131" s="2">
-        <v>1.6</v>
+        <v>-22.605904341776682</v>
       </c>
       <c r="H131" s="2">
-        <v>0.6</v>
+        <v>-7.0998959620521056</v>
       </c>
       <c r="I131" t="s">
+        <v>28</v>
+      </c>
+      <c r="J131" t="s">
+        <v>29</v>
+      </c>
+      <c r="K131" t="s">
         <v>154</v>
-      </c>
-      <c r="J131" t="s">
-        <v>155</v>
-      </c>
-      <c r="K131" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="132" spans="1:11">
       <c r="A132" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B132">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C132">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D132">
-        <v>8099</v>
+        <v>8101</v>
       </c>
       <c r="E132" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F132" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G132" s="2">
-        <v>0.8</v>
+        <v>3.4226509286685358</v>
       </c>
       <c r="H132" s="2">
-        <v>-0.1</v>
+        <v>29.4674455386726</v>
       </c>
       <c r="I132" t="s">
+        <v>28</v>
+      </c>
+      <c r="J132" t="s">
+        <v>29</v>
+      </c>
+      <c r="K132" t="s">
         <v>154</v>
-      </c>
-      <c r="J132" t="s">
-        <v>155</v>
-      </c>
-      <c r="K132" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="133" spans="1:11">
       <c r="A133" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B133">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C133">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D133">
-        <v>8100</v>
+        <v>8102</v>
       </c>
       <c r="E133" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F133" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G133" s="2">
-        <v>-0.5</v>
+        <v>2.8654861594613834</v>
       </c>
       <c r="H133" s="2">
-        <v>-0.3</v>
+        <v>-6.9318043726368961</v>
       </c>
       <c r="I133" t="s">
+        <v>28</v>
+      </c>
+      <c r="J133" t="s">
+        <v>29</v>
+      </c>
+      <c r="K133" t="s">
         <v>154</v>
-      </c>
-      <c r="J133" t="s">
-        <v>155</v>
-      </c>
-      <c r="K133" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="134" spans="1:11">
       <c r="A134" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B134">
         <v>2025</v>
       </c>
       <c r="C134">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D134">
-        <v>8101</v>
+        <v>8103</v>
       </c>
       <c r="E134" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F134" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G134" s="2">
-        <v>1.3</v>
+        <v>16.771586358363045</v>
       </c>
       <c r="H134" s="2">
-        <v>1.1000000000000001</v>
+        <v>4.3179650406290682</v>
       </c>
       <c r="I134" t="s">
+        <v>28</v>
+      </c>
+      <c r="J134" t="s">
+        <v>29</v>
+      </c>
+      <c r="K134" t="s">
         <v>154</v>
-      </c>
-      <c r="J134" t="s">
-        <v>155</v>
-      </c>
-      <c r="K134" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="135" spans="1:11">
       <c r="A135" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B135">
         <v>2025</v>
       </c>
       <c r="C135">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D135">
-        <v>8102</v>
+        <v>8104</v>
       </c>
       <c r="E135" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F135" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G135" s="2">
-        <v>3.9</v>
+        <v>32.673406348770669</v>
       </c>
       <c r="H135" s="2">
-        <v>3.2</v>
+        <v>5.5511330902374256</v>
       </c>
       <c r="I135" t="s">
+        <v>28</v>
+      </c>
+      <c r="J135" t="s">
+        <v>29</v>
+      </c>
+      <c r="K135" t="s">
         <v>154</v>
-      </c>
-      <c r="J135" t="s">
-        <v>155</v>
-      </c>
-      <c r="K135" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="136" spans="1:11">
       <c r="A136" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B136">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C136">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D136">
-        <v>8103</v>
+        <v>8105</v>
       </c>
       <c r="E136" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F136" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G136" s="2">
-        <v>4.3</v>
+        <v>4.4643082914077592</v>
       </c>
       <c r="H136" s="2">
-        <v>0.3</v>
+        <v>1.9400007632219607</v>
       </c>
       <c r="I136" t="s">
+        <v>28</v>
+      </c>
+      <c r="J136" t="s">
+        <v>29</v>
+      </c>
+      <c r="K136" t="s">
         <v>154</v>
-      </c>
-      <c r="J136" t="s">
-        <v>155</v>
-      </c>
-      <c r="K136" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="137" spans="1:11">
       <c r="A137" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B137">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C137">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D137">
-        <v>8104</v>
+        <v>8097</v>
       </c>
       <c r="E137" t="s">
+        <v>168</v>
+      </c>
+      <c r="F137" t="s">
         <v>170</v>
       </c>
-      <c r="F137" t="s">
-        <v>173</v>
-      </c>
       <c r="G137" s="2">
-        <v>5</v>
+        <v>2.7516280088027756</v>
       </c>
       <c r="H137" s="2">
-        <v>0.3</v>
+        <v>-1.2823170196623379</v>
       </c>
       <c r="I137" t="s">
+        <v>28</v>
+      </c>
+      <c r="J137" t="s">
+        <v>29</v>
+      </c>
+      <c r="K137" t="s">
         <v>154</v>
-      </c>
-      <c r="J137" t="s">
-        <v>155</v>
-      </c>
-      <c r="K137" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="138" spans="1:11">
       <c r="A138" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B138">
         <v>2024</v>
       </c>
       <c r="C138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D138">
-        <v>8097</v>
+        <v>8098</v>
       </c>
       <c r="E138" t="s">
+        <v>168</v>
+      </c>
+      <c r="F138" t="s">
         <v>170</v>
       </c>
-      <c r="F138" t="s">
-        <v>174</v>
-      </c>
       <c r="G138" s="2">
-        <v>-0.9</v>
+        <v>-0.53918481213897085</v>
       </c>
       <c r="H138" s="2">
-        <v>0.9</v>
+        <v>-0.45979944581669985</v>
       </c>
       <c r="I138" t="s">
+        <v>28</v>
+      </c>
+      <c r="J138" t="s">
+        <v>29</v>
+      </c>
+      <c r="K138" t="s">
         <v>154</v>
-      </c>
-      <c r="J138" t="s">
-        <v>155</v>
-      </c>
-      <c r="K138" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="139" spans="1:11">
       <c r="A139" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B139">
         <v>2024</v>
       </c>
       <c r="C139">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D139">
-        <v>8098</v>
+        <v>8099</v>
       </c>
       <c r="E139" t="s">
+        <v>168</v>
+      </c>
+      <c r="F139" t="s">
         <v>170</v>
       </c>
-      <c r="F139" t="s">
-        <v>174</v>
-      </c>
       <c r="G139" s="2">
-        <v>1.5</v>
+        <v>-1.0187498816592311</v>
       </c>
       <c r="H139" s="2">
-        <v>1</v>
+        <v>-9.0036271348059582E-2</v>
       </c>
       <c r="I139" t="s">
+        <v>28</v>
+      </c>
+      <c r="J139" t="s">
+        <v>29</v>
+      </c>
+      <c r="K139" t="s">
         <v>154</v>
-      </c>
-      <c r="J139" t="s">
-        <v>155</v>
-      </c>
-      <c r="K139" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="140" spans="1:11">
       <c r="A140" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B140">
         <v>2024</v>
       </c>
       <c r="C140">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D140">
-        <v>8099</v>
+        <v>8100</v>
       </c>
       <c r="E140" t="s">
+        <v>168</v>
+      </c>
+      <c r="F140" t="s">
         <v>170</v>
       </c>
-      <c r="F140" t="s">
-        <v>174</v>
-      </c>
       <c r="G140" s="2">
-        <v>2.4</v>
+        <v>-2.6400649413980348</v>
       </c>
       <c r="H140" s="2">
-        <v>0.1</v>
+        <v>-0.83052607385162291</v>
       </c>
       <c r="I140" t="s">
+        <v>28</v>
+      </c>
+      <c r="J140" t="s">
+        <v>29</v>
+      </c>
+      <c r="K140" t="s">
         <v>154</v>
-      </c>
-      <c r="J140" t="s">
-        <v>155</v>
-      </c>
-      <c r="K140" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="141" spans="1:11">
       <c r="A141" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B141">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C141">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D141">
-        <v>8100</v>
+        <v>8101</v>
       </c>
       <c r="E141" t="s">
+        <v>168</v>
+      </c>
+      <c r="F141" t="s">
         <v>170</v>
       </c>
-      <c r="F141" t="s">
-        <v>174</v>
-      </c>
       <c r="G141" s="2">
-        <v>2.5</v>
+        <v>1.652567767956592</v>
       </c>
       <c r="H141" s="2">
-        <v>0.4</v>
+        <v>3.0701792581754983</v>
       </c>
       <c r="I141" t="s">
+        <v>28</v>
+      </c>
+      <c r="J141" t="s">
+        <v>29</v>
+      </c>
+      <c r="K141" t="s">
         <v>154</v>
-      </c>
-      <c r="J141" t="s">
-        <v>155</v>
-      </c>
-      <c r="K141" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="142" spans="1:11">
       <c r="A142" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B142">
         <v>2025</v>
       </c>
       <c r="C142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D142">
-        <v>8101</v>
+        <v>8102</v>
       </c>
       <c r="E142" t="s">
+        <v>168</v>
+      </c>
+      <c r="F142" t="s">
         <v>170</v>
       </c>
-      <c r="F142" t="s">
-        <v>174</v>
-      </c>
       <c r="G142" s="2">
-        <v>2.6</v>
+        <v>3.7116882881407909</v>
       </c>
       <c r="H142" s="2">
-        <v>1</v>
+        <v>1.5565320059597543</v>
       </c>
       <c r="I142" t="s">
+        <v>28</v>
+      </c>
+      <c r="J142" t="s">
+        <v>29</v>
+      </c>
+      <c r="K142" t="s">
         <v>154</v>
-      </c>
-      <c r="J142" t="s">
-        <v>155</v>
-      </c>
-      <c r="K142" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="143" spans="1:11">
       <c r="A143" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B143">
         <v>2025</v>
       </c>
       <c r="C143">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D143">
-        <v>8102</v>
+        <v>8103</v>
       </c>
       <c r="E143" t="s">
+        <v>168</v>
+      </c>
+      <c r="F143" t="s">
         <v>170</v>
       </c>
-      <c r="F143" t="s">
-        <v>174</v>
-      </c>
       <c r="G143" s="2">
-        <v>1.2</v>
+        <v>4.0599238721654718</v>
       </c>
       <c r="H143" s="2">
-        <v>-0.4</v>
+        <v>0.24543415771554056</v>
       </c>
       <c r="I143" t="s">
+        <v>28</v>
+      </c>
+      <c r="J143" t="s">
+        <v>29</v>
+      </c>
+      <c r="K143" t="s">
         <v>154</v>
-      </c>
-      <c r="J143" t="s">
-        <v>155</v>
-      </c>
-      <c r="K143" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="144" spans="1:11">
       <c r="A144" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B144">
         <v>2025</v>
       </c>
       <c r="C144">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D144">
-        <v>8103</v>
+        <v>8104</v>
       </c>
       <c r="E144" t="s">
+        <v>168</v>
+      </c>
+      <c r="F144" t="s">
         <v>170</v>
       </c>
-      <c r="F144" t="s">
-        <v>174</v>
-      </c>
       <c r="G144" s="2">
-        <v>-0.1</v>
+        <v>5.131242136534242</v>
       </c>
       <c r="H144" s="2">
-        <v>-1.1000000000000001</v>
+        <v>0.1904440050371603</v>
       </c>
       <c r="I144" t="s">
+        <v>28</v>
+      </c>
+      <c r="J144" t="s">
+        <v>29</v>
+      </c>
+      <c r="K144" t="s">
         <v>154</v>
-      </c>
-      <c r="J144" t="s">
-        <v>155</v>
-      </c>
-      <c r="K144" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="145" spans="1:11">
       <c r="A145" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B145">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C145">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D145">
-        <v>8104</v>
+        <v>8105</v>
       </c>
       <c r="E145" t="s">
+        <v>168</v>
+      </c>
+      <c r="F145" t="s">
         <v>170</v>
       </c>
-      <c r="F145" t="s">
-        <v>174</v>
-      </c>
       <c r="G145" s="2">
-        <v>-0.6</v>
+        <v>6.4122642969431709</v>
       </c>
       <c r="H145" s="2">
-        <v>-0.1</v>
+        <v>4.3260874071115341</v>
       </c>
       <c r="I145" t="s">
+        <v>28</v>
+      </c>
+      <c r="J145" t="s">
+        <v>29</v>
+      </c>
+      <c r="K145" t="s">
         <v>154</v>
-      </c>
-      <c r="J145" t="s">
-        <v>155</v>
-      </c>
-      <c r="K145" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -33684,25 +33777,25 @@
         <v>8097</v>
       </c>
       <c r="E146" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F146" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G146" s="2">
-        <v>2.5</v>
+        <v>1.4260398260585117</v>
       </c>
       <c r="H146" s="2">
-        <v>-4.2</v>
+        <v>-0.72818579544939865</v>
       </c>
       <c r="I146" t="s">
+        <v>28</v>
+      </c>
+      <c r="J146" t="s">
+        <v>29</v>
+      </c>
+      <c r="K146" t="s">
         <v>154</v>
-      </c>
-      <c r="J146" t="s">
-        <v>155</v>
-      </c>
-      <c r="K146" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -33719,25 +33812,25 @@
         <v>8098</v>
       </c>
       <c r="E147" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F147" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G147" s="2">
-        <v>0.3</v>
+        <v>1.5530478713450258</v>
       </c>
       <c r="H147" s="2">
-        <v>0.4</v>
+        <v>0.62414991239232442</v>
       </c>
       <c r="I147" t="s">
+        <v>28</v>
+      </c>
+      <c r="J147" t="s">
+        <v>29</v>
+      </c>
+      <c r="K147" t="s">
         <v>154</v>
-      </c>
-      <c r="J147" t="s">
-        <v>155</v>
-      </c>
-      <c r="K147" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -33754,25 +33847,25 @@
         <v>8099</v>
       </c>
       <c r="E148" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F148" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G148" s="2">
-        <v>-5.5</v>
+        <v>0.83736626529127278</v>
       </c>
       <c r="H148" s="2">
-        <v>-3.6</v>
+        <v>-7.540196642767949E-2</v>
       </c>
       <c r="I148" t="s">
+        <v>28</v>
+      </c>
+      <c r="J148" t="s">
+        <v>29</v>
+      </c>
+      <c r="K148" t="s">
         <v>154</v>
-      </c>
-      <c r="J148" t="s">
-        <v>155</v>
-      </c>
-      <c r="K148" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -33789,25 +33882,25 @@
         <v>8100</v>
       </c>
       <c r="E149" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F149" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G149" s="2">
-        <v>-16.399999999999999</v>
+        <v>-0.51247996705240384</v>
       </c>
       <c r="H149" s="2">
-        <v>-9.8000000000000007</v>
+        <v>-0.32918439188104331</v>
       </c>
       <c r="I149" t="s">
+        <v>28</v>
+      </c>
+      <c r="J149" t="s">
+        <v>29</v>
+      </c>
+      <c r="K149" t="s">
         <v>154</v>
-      </c>
-      <c r="J149" t="s">
-        <v>155</v>
-      </c>
-      <c r="K149" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -33824,25 +33917,25 @@
         <v>8101</v>
       </c>
       <c r="E150" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F150" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G150" s="2">
-        <v>-15.5</v>
+        <v>1.3210009943700252</v>
       </c>
       <c r="H150" s="2">
-        <v>-3.2</v>
+        <v>1.1013198680713154</v>
       </c>
       <c r="I150" t="s">
+        <v>28</v>
+      </c>
+      <c r="J150" t="s">
+        <v>29</v>
+      </c>
+      <c r="K150" t="s">
         <v>154</v>
-      </c>
-      <c r="J150" t="s">
-        <v>155</v>
-      </c>
-      <c r="K150" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -33859,25 +33952,25 @@
         <v>8102</v>
       </c>
       <c r="E151" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F151" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G151" s="2">
-        <v>-24.5</v>
+        <v>3.8718613608252017</v>
       </c>
       <c r="H151" s="2">
-        <v>-10.3</v>
+        <v>3.1574663364377864</v>
       </c>
       <c r="I151" t="s">
+        <v>28</v>
+      </c>
+      <c r="J151" t="s">
+        <v>29</v>
+      </c>
+      <c r="K151" t="s">
         <v>154</v>
-      </c>
-      <c r="J151" t="s">
-        <v>155</v>
-      </c>
-      <c r="K151" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -33894,25 +33987,25 @@
         <v>8103</v>
       </c>
       <c r="E152" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F152" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G152" s="2">
-        <v>-27.6</v>
+        <v>4.286545164322364</v>
       </c>
       <c r="H152" s="2">
-        <v>-7.5</v>
+        <v>0.32352332318030808</v>
       </c>
       <c r="I152" t="s">
+        <v>28</v>
+      </c>
+      <c r="J152" t="s">
+        <v>29</v>
+      </c>
+      <c r="K152" t="s">
         <v>154</v>
-      </c>
-      <c r="J152" t="s">
-        <v>155</v>
-      </c>
-      <c r="K152" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -33929,589 +34022,2073 @@
         <v>8104</v>
       </c>
       <c r="E153" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F153" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G153" s="2">
-        <v>8.5</v>
+        <v>4.9669681308163849</v>
       </c>
       <c r="H153" s="2">
-        <v>35.200000000000003</v>
+        <v>0.32112300800546389</v>
       </c>
       <c r="I153" t="s">
+        <v>28</v>
+      </c>
+      <c r="J153" t="s">
+        <v>29</v>
+      </c>
+      <c r="K153" t="s">
         <v>154</v>
-      </c>
-      <c r="J153" t="s">
-        <v>155</v>
-      </c>
-      <c r="K153" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="154" spans="1:11">
       <c r="A154" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B154">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C154">
         <v>1</v>
       </c>
       <c r="D154">
-        <v>8097</v>
+        <v>8105</v>
       </c>
       <c r="E154" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F154" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G154" s="2">
-        <v>2.9</v>
+        <v>1.0780782954499246</v>
       </c>
       <c r="H154" s="2">
-        <v>0.3</v>
+        <v>-2.6443527199668582</v>
       </c>
       <c r="I154" t="s">
+        <v>28</v>
+      </c>
+      <c r="J154" t="s">
+        <v>29</v>
+      </c>
+      <c r="K154" t="s">
         <v>154</v>
-      </c>
-      <c r="J154" t="s">
-        <v>155</v>
-      </c>
-      <c r="K154" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="155" spans="1:11">
       <c r="A155" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B155">
         <v>2024</v>
       </c>
       <c r="C155">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D155">
-        <v>8098</v>
+        <v>8097</v>
       </c>
       <c r="E155" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F155" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G155" s="2">
-        <v>-1.3</v>
+        <v>-0.94305076162686241</v>
       </c>
       <c r="H155" s="2">
-        <v>-3.8</v>
+        <v>0.89814049528549322</v>
       </c>
       <c r="I155" t="s">
+        <v>28</v>
+      </c>
+      <c r="J155" t="s">
+        <v>29</v>
+      </c>
+      <c r="K155" t="s">
         <v>154</v>
-      </c>
-      <c r="J155" t="s">
-        <v>155</v>
-      </c>
-      <c r="K155" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="156" spans="1:11">
       <c r="A156" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B156">
         <v>2024</v>
       </c>
       <c r="C156">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D156">
-        <v>8099</v>
+        <v>8098</v>
       </c>
       <c r="E156" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F156" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G156" s="2">
-        <v>-5.2</v>
+        <v>1.5008054033873064</v>
       </c>
       <c r="H156" s="2">
-        <v>-1.6</v>
+        <v>1.0278115955862255</v>
       </c>
       <c r="I156" t="s">
+        <v>28</v>
+      </c>
+      <c r="J156" t="s">
+        <v>29</v>
+      </c>
+      <c r="K156" t="s">
         <v>154</v>
-      </c>
-      <c r="J156" t="s">
-        <v>155</v>
-      </c>
-      <c r="K156" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="157" spans="1:11">
       <c r="A157" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B157">
         <v>2024</v>
       </c>
       <c r="C157">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D157">
-        <v>8100</v>
+        <v>8099</v>
       </c>
       <c r="E157" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F157" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G157" s="2">
-        <v>-9</v>
+        <v>2.4478272123478861</v>
       </c>
       <c r="H157" s="2">
-        <v>-4.2</v>
+        <v>0.14437774852813501</v>
       </c>
       <c r="I157" t="s">
+        <v>28</v>
+      </c>
+      <c r="J157" t="s">
+        <v>29</v>
+      </c>
+      <c r="K157" t="s">
         <v>154</v>
-      </c>
-      <c r="J157" t="s">
-        <v>155</v>
-      </c>
-      <c r="K157" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="158" spans="1:11">
       <c r="A158" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B158">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C158">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D158">
-        <v>8101</v>
+        <v>8100</v>
       </c>
       <c r="E158" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F158" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G158" s="2">
-        <v>-7.8</v>
+        <v>2.4709476540267561</v>
       </c>
       <c r="H158" s="2">
-        <v>1.6</v>
+        <v>0.38066583436131562</v>
       </c>
       <c r="I158" t="s">
+        <v>28</v>
+      </c>
+      <c r="J158" t="s">
+        <v>29</v>
+      </c>
+      <c r="K158" t="s">
         <v>154</v>
-      </c>
-      <c r="J158" t="s">
-        <v>155</v>
-      </c>
-      <c r="K158" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="159" spans="1:11">
       <c r="A159" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B159">
         <v>2025</v>
       </c>
       <c r="C159">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D159">
-        <v>8102</v>
+        <v>8101</v>
       </c>
       <c r="E159" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F159" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G159" s="2">
-        <v>-2.9</v>
+        <v>2.6032765233592547</v>
       </c>
       <c r="H159" s="2">
-        <v>1.3</v>
+        <v>1.0284382738770637</v>
       </c>
       <c r="I159" t="s">
+        <v>28</v>
+      </c>
+      <c r="J159" t="s">
+        <v>29</v>
+      </c>
+      <c r="K159" t="s">
         <v>154</v>
-      </c>
-      <c r="J159" t="s">
-        <v>155</v>
-      </c>
-      <c r="K159" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="160" spans="1:11">
       <c r="A160" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B160">
         <v>2025</v>
       </c>
       <c r="C160">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D160">
-        <v>8103</v>
+        <v>8102</v>
       </c>
       <c r="E160" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F160" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G160" s="2">
-        <v>-18</v>
+        <v>1.184543725428866</v>
       </c>
       <c r="H160" s="2">
-        <v>-16.8</v>
+        <v>-0.36913667615009471</v>
       </c>
       <c r="I160" t="s">
+        <v>28</v>
+      </c>
+      <c r="J160" t="s">
+        <v>29</v>
+      </c>
+      <c r="K160" t="s">
         <v>154</v>
-      </c>
-      <c r="J160" t="s">
-        <v>155</v>
-      </c>
-      <c r="K160" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="161" spans="1:11">
       <c r="A161" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B161">
         <v>2025</v>
       </c>
       <c r="C161">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D161">
-        <v>8104</v>
+        <v>8103</v>
       </c>
       <c r="E161" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F161" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G161" s="2">
-        <v>2.9</v>
+        <v>-0.10885312953662352</v>
       </c>
       <c r="H161" s="2">
-        <v>20.2</v>
+        <v>-1.1357231290713088</v>
       </c>
       <c r="I161" t="s">
+        <v>28</v>
+      </c>
+      <c r="J161" t="s">
+        <v>29</v>
+      </c>
+      <c r="K161" t="s">
         <v>154</v>
-      </c>
-      <c r="J161" t="s">
-        <v>155</v>
-      </c>
-      <c r="K161" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="162" spans="1:11">
       <c r="A162" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B162">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C162">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D162">
-        <v>8097</v>
+        <v>8104</v>
       </c>
       <c r="E162" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="F162" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G162" s="2">
-        <v>-0.8</v>
+        <v>-0.61234624021897499</v>
       </c>
       <c r="H162" s="2">
-        <v>-0.6</v>
+        <v>-0.12529465640018778</v>
       </c>
       <c r="I162" t="s">
+        <v>28</v>
+      </c>
+      <c r="J162" t="s">
+        <v>29</v>
+      </c>
+      <c r="K162" t="s">
         <v>154</v>
-      </c>
-      <c r="J162" t="s">
-        <v>155</v>
-      </c>
-      <c r="K162" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="163" spans="1:11">
       <c r="A163" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B163">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C163">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163">
-        <v>8098</v>
+        <v>8105</v>
       </c>
       <c r="E163" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="F163" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G163" s="2">
-        <v>-3.8</v>
+        <v>-4.7747949733916943</v>
       </c>
       <c r="H163" s="2">
-        <v>-1</v>
+        <v>-3.2027280631805044</v>
       </c>
       <c r="I163" t="s">
+        <v>28</v>
+      </c>
+      <c r="J163" t="s">
+        <v>29</v>
+      </c>
+      <c r="K163" t="s">
         <v>154</v>
-      </c>
-      <c r="J163" t="s">
-        <v>155</v>
-      </c>
-      <c r="K163" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="164" spans="1:11">
       <c r="A164" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B164">
         <v>2024</v>
       </c>
       <c r="C164">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D164">
-        <v>8099</v>
+        <v>8097</v>
       </c>
       <c r="E164" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F164" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G164" s="2">
-        <v>-1.7</v>
+        <v>2.5469494140185622</v>
       </c>
       <c r="H164" s="2">
-        <v>-0.2</v>
+        <v>-4.2190154373598965</v>
       </c>
       <c r="I164" t="s">
+        <v>28</v>
+      </c>
+      <c r="J164" t="s">
+        <v>29</v>
+      </c>
+      <c r="K164" t="s">
         <v>154</v>
-      </c>
-      <c r="J164" t="s">
-        <v>155</v>
-      </c>
-      <c r="K164" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="165" spans="1:11">
       <c r="A165" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B165">
         <v>2024</v>
       </c>
       <c r="C165">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D165">
-        <v>8100</v>
+        <v>8098</v>
       </c>
       <c r="E165" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F165" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G165" s="2">
-        <v>-0.7</v>
+        <v>0.2503982174167696</v>
       </c>
       <c r="H165" s="2">
-        <v>1.2</v>
+        <v>0.4445154207306512</v>
       </c>
       <c r="I165" t="s">
+        <v>28</v>
+      </c>
+      <c r="J165" t="s">
+        <v>29</v>
+      </c>
+      <c r="K165" t="s">
         <v>154</v>
-      </c>
-      <c r="J165" t="s">
-        <v>155</v>
-      </c>
-      <c r="K165" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="166" spans="1:11">
       <c r="A166" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B166">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C166">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D166">
-        <v>8101</v>
+        <v>8099</v>
       </c>
       <c r="E166" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F166" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G166" s="2">
-        <v>3.5</v>
+        <v>-5.5115313812107436</v>
       </c>
       <c r="H166" s="2">
-        <v>3.6</v>
+        <v>-3.5868342600950065</v>
       </c>
       <c r="I166" t="s">
+        <v>28</v>
+      </c>
+      <c r="J166" t="s">
+        <v>29</v>
+      </c>
+      <c r="K166" t="s">
         <v>154</v>
-      </c>
-      <c r="J166" t="s">
-        <v>155</v>
-      </c>
-      <c r="K166" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="167" spans="1:11">
       <c r="A167" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B167">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C167">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D167">
-        <v>8102</v>
+        <v>8100</v>
       </c>
       <c r="E167" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F167" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G167" s="2">
-        <v>3.5</v>
+        <v>-16.360823106626931</v>
       </c>
       <c r="H167" s="2">
-        <v>-1.1000000000000001</v>
+        <v>-9.8287931939696431</v>
       </c>
       <c r="I167" t="s">
+        <v>28</v>
+      </c>
+      <c r="J167" t="s">
+        <v>29</v>
+      </c>
+      <c r="K167" t="s">
         <v>154</v>
-      </c>
-      <c r="J167" t="s">
-        <v>155</v>
-      </c>
-      <c r="K167" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="168" spans="1:11">
       <c r="A168" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B168">
         <v>2025</v>
       </c>
       <c r="C168">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D168">
-        <v>8103</v>
+        <v>8101</v>
       </c>
       <c r="E168" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F168" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G168" s="2">
-        <v>2.7</v>
+        <v>-15.493539068418293</v>
       </c>
       <c r="H168" s="2">
-        <v>-0.9</v>
+        <v>-3.2258287255754636</v>
       </c>
       <c r="I168" t="s">
+        <v>28</v>
+      </c>
+      <c r="J168" t="s">
+        <v>29</v>
+      </c>
+      <c r="K168" t="s">
         <v>154</v>
-      </c>
-      <c r="J168" t="s">
-        <v>155</v>
-      </c>
-      <c r="K168" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="169" spans="1:11">
       <c r="A169" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B169">
         <v>2025</v>
       </c>
       <c r="C169">
+        <v>2</v>
+      </c>
+      <c r="D169">
+        <v>8102</v>
+      </c>
+      <c r="E169" t="s">
+        <v>173</v>
+      </c>
+      <c r="F169" t="s">
+        <v>174</v>
+      </c>
+      <c r="G169" s="2">
+        <v>-24.531953581826105</v>
+      </c>
+      <c r="H169" s="2">
+        <v>-10.298558611277031</v>
+      </c>
+      <c r="I169" t="s">
+        <v>28</v>
+      </c>
+      <c r="J169" t="s">
+        <v>29</v>
+      </c>
+      <c r="K169" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11">
+      <c r="A170" t="s">
+        <v>131</v>
+      </c>
+      <c r="B170">
+        <v>2025</v>
+      </c>
+      <c r="C170">
+        <v>3</v>
+      </c>
+      <c r="D170">
+        <v>8103</v>
+      </c>
+      <c r="E170" t="s">
+        <v>173</v>
+      </c>
+      <c r="F170" t="s">
+        <v>174</v>
+      </c>
+      <c r="G170" s="2">
+        <v>-27.614120567187548</v>
+      </c>
+      <c r="H170" s="2">
+        <v>-7.524414342016339</v>
+      </c>
+      <c r="I170" t="s">
+        <v>28</v>
+      </c>
+      <c r="J170" t="s">
+        <v>29</v>
+      </c>
+      <c r="K170" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11">
+      <c r="A171" t="s">
+        <v>132</v>
+      </c>
+      <c r="B171">
+        <v>2025</v>
+      </c>
+      <c r="C171">
         <v>4</v>
       </c>
-      <c r="D169">
+      <c r="D171">
         <v>8104</v>
       </c>
-      <c r="E169" t="s">
-        <v>178</v>
-      </c>
-      <c r="F169" t="s">
-        <v>179</v>
-      </c>
-      <c r="G169" s="2">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="H169" s="2">
-        <v>3.1</v>
-      </c>
-      <c r="I169" t="s">
+      <c r="E171" t="s">
+        <v>173</v>
+      </c>
+      <c r="F171" t="s">
+        <v>174</v>
+      </c>
+      <c r="G171" s="2">
+        <v>8.5191561955241024</v>
+      </c>
+      <c r="H171" s="2">
+        <v>35.182487971360409</v>
+      </c>
+      <c r="I171" t="s">
+        <v>28</v>
+      </c>
+      <c r="J171" t="s">
+        <v>29</v>
+      </c>
+      <c r="K171" t="s">
         <v>154</v>
       </c>
-      <c r="J169" t="s">
-        <v>155</v>
-      </c>
-      <c r="K169" t="s">
-        <v>156</v>
+    </row>
+    <row r="172" spans="1:11">
+      <c r="A172" t="s">
+        <v>133</v>
+      </c>
+      <c r="B172">
+        <v>2026</v>
+      </c>
+      <c r="C172">
+        <v>1</v>
+      </c>
+      <c r="D172">
+        <v>8105</v>
+      </c>
+      <c r="E172" t="s">
+        <v>173</v>
+      </c>
+      <c r="F172" t="s">
+        <v>174</v>
+      </c>
+      <c r="G172" s="2">
+        <v>9.3818717701505072</v>
+      </c>
+      <c r="H172" s="2">
+        <v>-2.4564845129317003</v>
+      </c>
+      <c r="I172" t="s">
+        <v>28</v>
+      </c>
+      <c r="J172" t="s">
+        <v>29</v>
+      </c>
+      <c r="K172" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11">
+      <c r="A173" t="s">
+        <v>125</v>
+      </c>
+      <c r="B173">
+        <v>2024</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="D173">
+        <v>8097</v>
+      </c>
+      <c r="E173" t="s">
+        <v>173</v>
+      </c>
+      <c r="F173" t="s">
+        <v>175</v>
+      </c>
+      <c r="G173" s="2">
+        <v>2.9176612027935089</v>
+      </c>
+      <c r="H173" s="2">
+        <v>0.2918034641987477</v>
+      </c>
+      <c r="I173" t="s">
+        <v>28</v>
+      </c>
+      <c r="J173" t="s">
+        <v>29</v>
+      </c>
+      <c r="K173" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11">
+      <c r="A174" t="s">
+        <v>126</v>
+      </c>
+      <c r="B174">
+        <v>2024</v>
+      </c>
+      <c r="C174">
+        <v>2</v>
+      </c>
+      <c r="D174">
+        <v>8098</v>
+      </c>
+      <c r="E174" t="s">
+        <v>173</v>
+      </c>
+      <c r="F174" t="s">
+        <v>175</v>
+      </c>
+      <c r="G174" s="2">
+        <v>-1.2620304218740275</v>
+      </c>
+      <c r="H174" s="2">
+        <v>-3.7839365555502602</v>
+      </c>
+      <c r="I174" t="s">
+        <v>28</v>
+      </c>
+      <c r="J174" t="s">
+        <v>29</v>
+      </c>
+      <c r="K174" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11">
+      <c r="A175" t="s">
+        <v>127</v>
+      </c>
+      <c r="B175">
+        <v>2024</v>
+      </c>
+      <c r="C175">
+        <v>3</v>
+      </c>
+      <c r="D175">
+        <v>8099</v>
+      </c>
+      <c r="E175" t="s">
+        <v>173</v>
+      </c>
+      <c r="F175" t="s">
+        <v>175</v>
+      </c>
+      <c r="G175" s="2">
+        <v>-5.1932775224284526</v>
+      </c>
+      <c r="H175" s="2">
+        <v>-1.5773663130302928</v>
+      </c>
+      <c r="I175" t="s">
+        <v>28</v>
+      </c>
+      <c r="J175" t="s">
+        <v>29</v>
+      </c>
+      <c r="K175" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11">
+      <c r="A176" t="s">
+        <v>128</v>
+      </c>
+      <c r="B176">
+        <v>2024</v>
+      </c>
+      <c r="C176">
+        <v>4</v>
+      </c>
+      <c r="D176">
+        <v>8100</v>
+      </c>
+      <c r="E176" t="s">
+        <v>173</v>
+      </c>
+      <c r="F176" t="s">
+        <v>175</v>
+      </c>
+      <c r="G176" s="2">
+        <v>-9.0133527231565314</v>
+      </c>
+      <c r="H176" s="2">
+        <v>-4.1990854956578838</v>
+      </c>
+      <c r="I176" t="s">
+        <v>28</v>
+      </c>
+      <c r="J176" t="s">
+        <v>29</v>
+      </c>
+      <c r="K176" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11">
+      <c r="A177" t="s">
+        <v>129</v>
+      </c>
+      <c r="B177">
+        <v>2025</v>
+      </c>
+      <c r="C177">
+        <v>1</v>
+      </c>
+      <c r="D177">
+        <v>8101</v>
+      </c>
+      <c r="E177" t="s">
+        <v>173</v>
+      </c>
+      <c r="F177" t="s">
+        <v>175</v>
+      </c>
+      <c r="G177" s="2">
+        <v>-7.7893338763095237</v>
+      </c>
+      <c r="H177" s="2">
+        <v>1.6410020696923322</v>
+      </c>
+      <c r="I177" t="s">
+        <v>28</v>
+      </c>
+      <c r="J177" t="s">
+        <v>29</v>
+      </c>
+      <c r="K177" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11">
+      <c r="A178" t="s">
+        <v>130</v>
+      </c>
+      <c r="B178">
+        <v>2025</v>
+      </c>
+      <c r="C178">
+        <v>2</v>
+      </c>
+      <c r="D178">
+        <v>8102</v>
+      </c>
+      <c r="E178" t="s">
+        <v>173</v>
+      </c>
+      <c r="F178" t="s">
+        <v>175</v>
+      </c>
+      <c r="G178" s="2">
+        <v>-2.9183087332260826</v>
+      </c>
+      <c r="H178" s="2">
+        <v>1.2986735578801811</v>
+      </c>
+      <c r="I178" t="s">
+        <v>28</v>
+      </c>
+      <c r="J178" t="s">
+        <v>29</v>
+      </c>
+      <c r="K178" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11">
+      <c r="A179" t="s">
+        <v>131</v>
+      </c>
+      <c r="B179">
+        <v>2025</v>
+      </c>
+      <c r="C179">
+        <v>3</v>
+      </c>
+      <c r="D179">
+        <v>8103</v>
+      </c>
+      <c r="E179" t="s">
+        <v>173</v>
+      </c>
+      <c r="F179" t="s">
+        <v>175</v>
+      </c>
+      <c r="G179" s="2">
+        <v>-17.98267073230533</v>
+      </c>
+      <c r="H179" s="2">
+        <v>-16.849805054223989</v>
+      </c>
+      <c r="I179" t="s">
+        <v>28</v>
+      </c>
+      <c r="J179" t="s">
+        <v>29</v>
+      </c>
+      <c r="K179" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11">
+      <c r="A180" t="s">
+        <v>132</v>
+      </c>
+      <c r="B180">
+        <v>2025</v>
+      </c>
+      <c r="C180">
+        <v>4</v>
+      </c>
+      <c r="D180">
+        <v>8104</v>
+      </c>
+      <c r="E180" t="s">
+        <v>173</v>
+      </c>
+      <c r="F180" t="s">
+        <v>175</v>
+      </c>
+      <c r="G180" s="2">
+        <v>2.9438723061007144</v>
+      </c>
+      <c r="H180" s="2">
+        <v>20.244309313631838</v>
+      </c>
+      <c r="I180" t="s">
+        <v>28</v>
+      </c>
+      <c r="J180" t="s">
+        <v>29</v>
+      </c>
+      <c r="K180" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11">
+      <c r="A181" t="s">
+        <v>133</v>
+      </c>
+      <c r="B181">
+        <v>2026</v>
+      </c>
+      <c r="C181">
+        <v>1</v>
+      </c>
+      <c r="D181">
+        <v>8105</v>
+      </c>
+      <c r="E181" t="s">
+        <v>173</v>
+      </c>
+      <c r="F181" t="s">
+        <v>175</v>
+      </c>
+      <c r="G181" s="2">
+        <v>3.9766291050041147</v>
+      </c>
+      <c r="H181" s="2">
+        <v>2.6606881722580411</v>
+      </c>
+      <c r="I181" t="s">
+        <v>28</v>
+      </c>
+      <c r="J181" t="s">
+        <v>29</v>
+      </c>
+      <c r="K181" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11">
+      <c r="A182" t="s">
+        <v>125</v>
+      </c>
+      <c r="B182">
+        <v>2024</v>
+      </c>
+      <c r="C182">
+        <v>1</v>
+      </c>
+      <c r="D182">
+        <v>8097</v>
+      </c>
+      <c r="E182" t="s">
+        <v>176</v>
+      </c>
+      <c r="F182" t="s">
+        <v>177</v>
+      </c>
+      <c r="G182" s="2">
+        <v>-0.84957514984074223</v>
+      </c>
+      <c r="H182" s="2">
+        <v>-0.59167100111118254</v>
+      </c>
+      <c r="I182" t="s">
+        <v>28</v>
+      </c>
+      <c r="J182" t="s">
+        <v>29</v>
+      </c>
+      <c r="K182" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11">
+      <c r="A183" t="s">
+        <v>126</v>
+      </c>
+      <c r="B183">
+        <v>2024</v>
+      </c>
+      <c r="C183">
+        <v>2</v>
+      </c>
+      <c r="D183">
+        <v>8098</v>
+      </c>
+      <c r="E183" t="s">
+        <v>176</v>
+      </c>
+      <c r="F183" t="s">
+        <v>177</v>
+      </c>
+      <c r="G183" s="2">
+        <v>-3.7517685133096279</v>
+      </c>
+      <c r="H183" s="2">
+        <v>-1.0414169427806153</v>
+      </c>
+      <c r="I183" t="s">
+        <v>28</v>
+      </c>
+      <c r="J183" t="s">
+        <v>29</v>
+      </c>
+      <c r="K183" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11">
+      <c r="A184" t="s">
+        <v>127</v>
+      </c>
+      <c r="B184">
+        <v>2024</v>
+      </c>
+      <c r="C184">
+        <v>3</v>
+      </c>
+      <c r="D184">
+        <v>8099</v>
+      </c>
+      <c r="E184" t="s">
+        <v>176</v>
+      </c>
+      <c r="F184" t="s">
+        <v>177</v>
+      </c>
+      <c r="G184" s="2">
+        <v>-1.7063500759741279</v>
+      </c>
+      <c r="H184" s="2">
+        <v>-0.22242537873885526</v>
+      </c>
+      <c r="I184" t="s">
+        <v>28</v>
+      </c>
+      <c r="J184" t="s">
+        <v>29</v>
+      </c>
+      <c r="K184" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11">
+      <c r="A185" t="s">
+        <v>128</v>
+      </c>
+      <c r="B185">
+        <v>2024</v>
+      </c>
+      <c r="C185">
+        <v>4</v>
+      </c>
+      <c r="D185">
+        <v>8100</v>
+      </c>
+      <c r="E185" t="s">
+        <v>176</v>
+      </c>
+      <c r="F185" t="s">
+        <v>177</v>
+      </c>
+      <c r="G185" s="2">
+        <v>-0.67673657812218346</v>
+      </c>
+      <c r="H185" s="2">
+        <v>1.19097856857735</v>
+      </c>
+      <c r="I185" t="s">
+        <v>28</v>
+      </c>
+      <c r="J185" t="s">
+        <v>29</v>
+      </c>
+      <c r="K185" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11">
+      <c r="A186" t="s">
+        <v>129</v>
+      </c>
+      <c r="B186">
+        <v>2025</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+      <c r="D186">
+        <v>8101</v>
+      </c>
+      <c r="E186" t="s">
+        <v>176</v>
+      </c>
+      <c r="F186" t="s">
+        <v>177</v>
+      </c>
+      <c r="G186" s="2">
+        <v>3.500855490192234</v>
+      </c>
+      <c r="H186" s="2">
+        <v>3.5894989729985616</v>
+      </c>
+      <c r="I186" t="s">
+        <v>28</v>
+      </c>
+      <c r="J186" t="s">
+        <v>29</v>
+      </c>
+      <c r="K186" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11">
+      <c r="A187" t="s">
+        <v>130</v>
+      </c>
+      <c r="B187">
+        <v>2025</v>
+      </c>
+      <c r="C187">
+        <v>2</v>
+      </c>
+      <c r="D187">
+        <v>8102</v>
+      </c>
+      <c r="E187" t="s">
+        <v>176</v>
+      </c>
+      <c r="F187" t="s">
+        <v>177</v>
+      </c>
+      <c r="G187" s="2">
+        <v>3.4563187104093451</v>
+      </c>
+      <c r="H187" s="2">
+        <v>-1.0839991668634252</v>
+      </c>
+      <c r="I187" t="s">
+        <v>28</v>
+      </c>
+      <c r="J187" t="s">
+        <v>29</v>
+      </c>
+      <c r="K187" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11">
+      <c r="A188" t="s">
+        <v>131</v>
+      </c>
+      <c r="B188">
+        <v>2025</v>
+      </c>
+      <c r="C188">
+        <v>3</v>
+      </c>
+      <c r="D188">
+        <v>8103</v>
+      </c>
+      <c r="E188" t="s">
+        <v>176</v>
+      </c>
+      <c r="F188" t="s">
+        <v>177</v>
+      </c>
+      <c r="G188" s="2">
+        <v>2.7118603259756568</v>
+      </c>
+      <c r="H188" s="2">
+        <v>-0.94041199310098689</v>
+      </c>
+      <c r="I188" t="s">
+        <v>28</v>
+      </c>
+      <c r="J188" t="s">
+        <v>29</v>
+      </c>
+      <c r="K188" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11">
+      <c r="A189" t="s">
+        <v>132</v>
+      </c>
+      <c r="B189">
+        <v>2025</v>
+      </c>
+      <c r="C189">
+        <v>4</v>
+      </c>
+      <c r="D189">
+        <v>8104</v>
+      </c>
+      <c r="E189" t="s">
+        <v>176</v>
+      </c>
+      <c r="F189" t="s">
+        <v>177</v>
+      </c>
+      <c r="G189" s="2">
+        <v>4.6212196182686238</v>
+      </c>
+      <c r="H189" s="2">
+        <v>3.0720654714232687</v>
+      </c>
+      <c r="I189" t="s">
+        <v>28</v>
+      </c>
+      <c r="J189" t="s">
+        <v>29</v>
+      </c>
+      <c r="K189" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11">
+      <c r="A190" t="s">
+        <v>133</v>
+      </c>
+      <c r="B190">
+        <v>2026</v>
+      </c>
+      <c r="C190">
+        <v>1</v>
+      </c>
+      <c r="D190">
+        <v>8105</v>
+      </c>
+      <c r="E190" t="s">
+        <v>176</v>
+      </c>
+      <c r="F190" t="s">
+        <v>177</v>
+      </c>
+      <c r="G190" s="2">
+        <v>2.1133620912766826</v>
+      </c>
+      <c r="H190" s="2">
+        <v>1.1063726467652746</v>
+      </c>
+      <c r="I190" t="s">
+        <v>28</v>
+      </c>
+      <c r="J190" t="s">
+        <v>29</v>
+      </c>
+      <c r="K190" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:H169">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF4CCCC"/>
+        <color rgb="FFFFF2CC"/>
+        <color rgb="FFD9EAD3"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:H190">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF4CCCC"/>
+        <color rgb="FFFFF2CC"/>
+        <color rgb="FFD9EAD3"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="44" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2">
+        <v>2018</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1.0442944970978418</v>
+      </c>
+      <c r="H2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3">
+        <v>2019</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.16540446460038272</v>
+      </c>
+      <c r="H3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4">
+        <v>2020</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="2">
+        <v>-9.2450962086545694</v>
+      </c>
+      <c r="H4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5">
+        <v>2021</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="2">
+        <v>9.8184171062300596</v>
+      </c>
+      <c r="H5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6">
+        <v>2022</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="2">
+        <v>6.1861393529674791</v>
+      </c>
+      <c r="H6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7">
+        <v>2023</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2.3552179820603536</v>
+      </c>
+      <c r="H7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C8">
+        <v>2024</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H8" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9">
+        <v>2025</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="H9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10">
+        <v>2025</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="H10" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>188</v>
+      </c>
+      <c r="B11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11">
+        <v>2025</v>
+      </c>
+      <c r="D11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="H11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12">
+        <v>2025</v>
+      </c>
+      <c r="D12" t="s">
+        <v>191</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="H12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C13">
+        <v>2025</v>
+      </c>
+      <c r="D13" t="s">
+        <v>192</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="H13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14">
+        <v>2026</v>
+      </c>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="H14" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>188</v>
+      </c>
+      <c r="B15" t="s">
+        <v>186</v>
+      </c>
+      <c r="C15">
+        <v>2026</v>
+      </c>
+      <c r="D15" t="s">
+        <v>190</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="H15" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C16">
+        <v>2026</v>
+      </c>
+      <c r="D16" t="s">
+        <v>191</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
+      </c>
+      <c r="H16" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>188</v>
+      </c>
+      <c r="B17" t="s">
+        <v>186</v>
+      </c>
+      <c r="C17">
+        <v>2026</v>
+      </c>
+      <c r="D17" t="s">
+        <v>192</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="H17" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B18" t="s">
+        <v>194</v>
+      </c>
+      <c r="C18">
+        <v>2026</v>
+      </c>
+      <c r="D18" t="s">
+        <v>191</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>195</v>
+      </c>
+      <c r="H18" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>193</v>
+      </c>
+      <c r="B19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19">
+        <v>2026</v>
+      </c>
+      <c r="D19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E19" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>197</v>
+      </c>
+      <c r="H19" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>193</v>
+      </c>
+      <c r="B20" t="s">
+        <v>194</v>
+      </c>
+      <c r="C20">
+        <v>2026</v>
+      </c>
+      <c r="D20" t="s">
+        <v>190</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>198</v>
+      </c>
+      <c r="G20" t="s">
+        <v>199</v>
+      </c>
+      <c r="H20" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" t="s">
+        <v>200</v>
+      </c>
+      <c r="C21">
+        <v>2026</v>
+      </c>
+      <c r="D21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E21" s="2">
+        <v>4</v>
+      </c>
+      <c r="F21" t="s">
+        <v>195</v>
+      </c>
+      <c r="H21" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>193</v>
+      </c>
+      <c r="B22" t="s">
+        <v>200</v>
+      </c>
+      <c r="C22">
+        <v>2026</v>
+      </c>
+      <c r="D22" t="s">
+        <v>192</v>
+      </c>
+      <c r="E22" s="2">
+        <v>3.3000000000000003</v>
+      </c>
+      <c r="F22" t="s">
+        <v>197</v>
+      </c>
+      <c r="H22" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>193</v>
+      </c>
+      <c r="B23" t="s">
+        <v>200</v>
+      </c>
+      <c r="C23">
+        <v>2026</v>
+      </c>
+      <c r="D23" t="s">
+        <v>190</v>
+      </c>
+      <c r="E23" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>198</v>
+      </c>
+      <c r="G23" t="s">
+        <v>201</v>
+      </c>
+      <c r="H23" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24">
+        <v>2026</v>
+      </c>
+      <c r="D24" t="s">
+        <v>191</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2</v>
+      </c>
+      <c r="F24" t="s">
+        <v>195</v>
+      </c>
+      <c r="H24" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>193</v>
+      </c>
+      <c r="B25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C25">
+        <v>2026</v>
+      </c>
+      <c r="D25" t="s">
+        <v>192</v>
+      </c>
+      <c r="E25" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="F25" t="s">
+        <v>197</v>
+      </c>
+      <c r="H25" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>193</v>
+      </c>
+      <c r="B26" t="s">
+        <v>186</v>
+      </c>
+      <c r="C26">
+        <v>2026</v>
+      </c>
+      <c r="D26" t="s">
+        <v>190</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="F26" t="s">
+        <v>198</v>
+      </c>
+      <c r="H26" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27" t="s">
+        <v>202</v>
+      </c>
+      <c r="C27">
+        <v>2026</v>
+      </c>
+      <c r="D27" t="s">
+        <v>191</v>
+      </c>
+      <c r="E27" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="F27" t="s">
+        <v>195</v>
+      </c>
+      <c r="H27" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>193</v>
+      </c>
+      <c r="B28" t="s">
+        <v>202</v>
+      </c>
+      <c r="C28">
+        <v>2026</v>
+      </c>
+      <c r="D28" t="s">
+        <v>192</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="F28" t="s">
+        <v>197</v>
+      </c>
+      <c r="H28" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>193</v>
+      </c>
+      <c r="B29" t="s">
+        <v>202</v>
+      </c>
+      <c r="C29">
+        <v>2026</v>
+      </c>
+      <c r="D29" t="s">
+        <v>190</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F29" t="s">
+        <v>198</v>
+      </c>
+      <c r="G29" t="s">
+        <v>199</v>
+      </c>
+      <c r="H29" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>193</v>
+      </c>
+      <c r="B30" t="s">
+        <v>203</v>
+      </c>
+      <c r="C30">
+        <v>2026</v>
+      </c>
+      <c r="D30" t="s">
+        <v>191</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2.1999999999999997</v>
+      </c>
+      <c r="F30" t="s">
+        <v>195</v>
+      </c>
+      <c r="H30" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>193</v>
+      </c>
+      <c r="B31" t="s">
+        <v>203</v>
+      </c>
+      <c r="C31">
+        <v>2026</v>
+      </c>
+      <c r="D31" t="s">
+        <v>192</v>
+      </c>
+      <c r="E31" s="2">
+        <v>2</v>
+      </c>
+      <c r="F31" t="s">
+        <v>197</v>
+      </c>
+      <c r="H31" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" t="s">
+        <v>203</v>
+      </c>
+      <c r="C32">
+        <v>2026</v>
+      </c>
+      <c r="D32" t="s">
+        <v>190</v>
+      </c>
+      <c r="E32" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="F32" t="s">
+        <v>198</v>
+      </c>
+      <c r="G32" t="s">
+        <v>199</v>
+      </c>
+      <c r="H32" t="s">
+        <v>196</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E2:E32">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
